--- a/results/ALL_GSE13425_13_5_5.xlsx
+++ b/results/ALL_GSE13425_13_5_5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="78">
   <si>
     <t>classifier</t>
   </si>
@@ -70,208 +70,184 @@
     <t>log_loss</t>
   </si>
   <si>
+    <t>RND_FST</t>
+  </si>
+  <si>
     <t>POM_enGROUPS</t>
   </si>
   <si>
     <t>POM_ENTROPY</t>
   </si>
   <si>
-    <t>RND_FST</t>
-  </si>
-  <si>
     <t>POM_ALG</t>
   </si>
   <si>
+    <t>SVC</t>
+  </si>
+  <si>
+    <t>3NN_OVO</t>
+  </si>
+  <si>
     <t>BAGGNG</t>
   </si>
   <si>
-    <t>SVC</t>
+    <t>7NN_MUL</t>
   </si>
   <si>
     <t>7NN_OVR</t>
   </si>
   <si>
+    <t>3NN_OVR</t>
+  </si>
+  <si>
+    <t>3NN_MUL</t>
+  </si>
+  <si>
     <t>5NN_OVR</t>
   </si>
   <si>
     <t>5NN_MUL</t>
   </si>
   <si>
-    <t>7NN_MUL</t>
-  </si>
-  <si>
-    <t>3NN_OVR</t>
-  </si>
-  <si>
-    <t>3NN_MUL</t>
-  </si>
-  <si>
-    <t>3NN_OVO</t>
+    <t>DEC_TRE</t>
+  </si>
+  <si>
+    <t>1NN_MUL</t>
+  </si>
+  <si>
+    <t>1NN_OVR</t>
+  </si>
+  <si>
+    <t>1NN_OVO</t>
+  </si>
+  <si>
+    <t>MLP</t>
+  </si>
+  <si>
+    <t>7NN_OVO</t>
   </si>
   <si>
     <t>5NN_OVO</t>
   </si>
   <si>
-    <t>7NN_OVO</t>
-  </si>
-  <si>
-    <t>1NN_OVO</t>
-  </si>
-  <si>
-    <t>1NN_MUL</t>
-  </si>
-  <si>
-    <t>1NN_OVR</t>
-  </si>
-  <si>
-    <t>DEC_TRE</t>
-  </si>
-  <si>
-    <t>MLP</t>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A8</t>
   </si>
   <si>
     <t>A1</t>
   </si>
   <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
     <t>A2</t>
   </si>
   <si>
-    <t>A10</t>
-  </si>
-  <si>
-    <t>A5</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
     <t>A9</t>
   </si>
   <si>
     <t>A4</t>
   </si>
   <si>
-    <t>A8</t>
-  </si>
-  <si>
     <t>xuyager</t>
   </si>
   <si>
+    <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9447727669874642, 2.8019991880170134, 1.6458236147674554, 1.546234683801399, 2.4114800788797277, 1.5862320192681403, 2.3923432772357724, 2.393026016915189, 2.0791362436201997, 2.046818746879295, 2.5800075972130534, 2.0180488437475006, 2.8834421649764375, 1.5753822490055667, 2.0849653751081907, 2.416341245824442, 2.3366857050063246, 2.4802537245617033, 1.2468230666848195, 2.4452083668769267], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.9216185665281814, 1.6400885383327464, 0.9124798945245478, 0.8148475885275268, 0.8921122680772945, 0.8215033526867803, 1.2486139599804753, 0.8622413083052717, 0.856065248270181, 1.2543180212300291, 1.3002760634976653, 1.2780742615017548, 1.2988354551569303, 1.237884720400324, 0.9018064245023566, 0.9111435324499801, 1.200963169741228, 1.2381554711622547, 0.8768566187998464, 0.8632538456240632], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.9291839306401382, 1.6227141527911777, 0.8818797901483901, 0.8291400339495646, 0.8703516058203228, 0.8304798346978411, 0.8406733995535693, 0.8451058670630862, 0.8729350179182653, 0.8628147670219878, 1.2857613740113505, 0.8736633549249033, 1.2633918505499842, 0.8855071843852161, 0.8886872461444426, 0.8588699465422046, 0.8354950012306536, 0.858157058275449, 0.8986754409707841, 0.8533209984299027], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.2341725147731233, 2.240505741794485, 2.2724576777645447, 4.4580096468753, 3.6616919494426834, 2.6932937765647726, 2.678091156807596, 4.575334491226991, 2.2868969942545916, 1.6493523116809676, 3.901641229560317, 0.5740182725204063, 0.610669725553231, 4.680062016438082, 0.6651768927194867, 5.30775012758612, 2.7673235603888915, 3.3728728756693633, 0.5904033614379076, 0.5992450621165876], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [2.75871661563757, 2.640061686294103, 2.8446195086208035, 0.635065571256506, 4.186697995182309, 0.4739601907566424, 0.5819830661049413, 0.5799994800247998, 3.8100869562272224, 2.641985620287596, 3.481178891169509, 2.3970415615505827, 3.903225534427142, 2.2647203019962774, 3.4482210882898605, 2.554344031709773, 2.4348052644193716, 1.99542081795396, 2.9172492917487056, 2.200485088284743], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.7945314949122055, 3.4018899899138213, 0.6136137856582025, 2.301085862198831, 0.5097745291109792, 2.137822273635953, 0.49444190698412244, 0.5395169119538139, 0.5489289959020404, 3.293271532828209, 3.251648927549524, 0.550219540405023, 2.689148293586088, 0.5292784202302115, 0.6284554290592425, 3.0006078797842104, 0.6254097435811034, 0.5437023815862057, 0.5217696925411303, 2.161240938424042], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.9112674278110563, 0.9408668515755663, 0.826895255531877, 0.7177162636869742, 0.8047028685079268, 0.7750599402342997, 0.8268239536798073, 0.7889847287564593, 0.842735118434121, 0.7018609127523037, 0.8143220596839099, 0.8152819065565253, 0.8260321336129692, 0.7314143442944568, 0.8136526107180247, 0.7663517344958745, 0.8403989265912932, 0.7636647837986532, 0.8020069147318423, 0.7427683933231543], \'SVC(C=1, random_state=13)\': [1.1171986522337094, 1.143277602854134, 1.148062513252707, 1.031392354680479, 1.0784274284575663, 1.0213250995254632, 1.0907405600669178, 1.0213231799430311, 1.100190194156102, 1.0099927457695217, 1.0908201516488356, 1.0692788688746808, 1.101366927716333, 1.0210313936659425, 1.1466307015718091, 1.0789114004897895, 1.1245827634031087, 1.0336193183941513, 1.0777612118297095, 1.0333905257517086], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9364724275918026, 0.9432191276782146, 0.8284826524264565, 0.7549054769820758, 0.8297112930007314, 0.8008662237008366, 0.8403227603103225, 0.7792748413515256, 0.8439371683691516, 0.775513865917793, 0.8398726570168208, 0.8287383659096759, 0.8397570028556799, 0.7803510674792085, 0.8505900613132106, 0.780170821358957, 0.8535496745986705, 0.7776515113420084, 0.8145012620258045, 0.7682934094718228], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [10.896918466477281, 14.41746135564687, 12.154255212609277, 8.056816639920306, 9.220469471634622, 11.025117507259369, 10.058693969055952, 8.480859620968744, 9.639581720345289, 9.752988564114055, 10.896918466477281, 8.480859620968745, 10.058693969055952, 9.752988564114057, 11.316030715187944, 8.90490260201718, 11.73514296389861, 10.177031545162492, 9.220469471634622, 10.60107452621093], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [5.757945419665684, 5.8235277178950025, 7.3953071598511135, 3.6408467964979123, 4.091531845955065, 5.819530093499816, 4.507298954288384, 3.694545010515181, 5.737717007246045, 5.372408777086395, 6.0929564484760075, 3.73531837407753, 5.299139916284545, 3.3242002434840128, 6.150138975202017, 4.906819879128347, 6.12656542240503, 4.940824252750654, 5.292449635529854, 6.17756313950123], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.215700156947808, 3.8371325603013533, 4.640842233517311, 2.921865497811883, 3.3570070156832625, 3.818454330929273, 4.252667393502782, 2.5576633146675953, 3.839902076850281, 3.383631458917611, 4.991312511305266, 3.0152987807120333, 3.347012925185231, 2.621528290222923, 4.210036097678636, 3.3568212404896487, 3.360076382495292, 2.5884844341187394, 3.798377699891472, 3.8326964940238653], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.4507013173064185, 2.848688521627796, 2.77049847647797, 1.2321636342994973, 2.8346193214086424, 2.472201170709748, 2.468340353491126, 2.020406109109224, 2.470742237614099, 1.6622660433074683, 3.6317367012692015, 2.3629277360725496, 2.471680177646263, 2.055310220439726, 2.490304576952541, 1.3700630363312163, 2.395363035117345, 1.2343791754807727, 3.295544066658845, 2.371612860109013], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.2876800271365385, 1.2658538198088465, 1.6155460661769019, 0.8891281084268284, 0.8604466336650688, 0.8327744514219056, 1.269085135073887, 0.8517683070569572, 1.2969057726816378, 0.8613626866463661, 0.8752463649208391, 1.2429679149866937, 0.901620510317477, 0.8551193634156518, 1.3015725191346916, 0.9164283659050546, 1.6605278826344883, 0.8547465705010743, 1.2760501461286906, 0.8887450535093594], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [1.2943204054986868, 0.8560923204819865, 0.8769678825170599, 0.8726498664365719, 0.8551552819886147, 0.8409595520476546, 1.2445651196027112, 0.870702528986893, 0.8886979906500823, 0.8379244067396873, 0.8784198832601995, 0.8702115083841507, 0.8779966450953229, 0.8809705681830606, 0.90640540750931, 0.8948271909521106, 0.9129244479177803, 0.8466118610370713, 0.8940090259098938, 0.8508323639694254], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.8734307261953447, 3.991175512584563, 0.6146523400175986, 1.6550914748949117, 2.4455740897973866, 3.0081009194066177, 3.7752779974958157, 1.629597475818563, 0.7159939869784093, 3.1536069828688795, 6.410205981459273, 3.8181415403534817, 3.5463724504434184, 0.5280118082446285, 3.4573909405148697, 2.3678393725002733, 2.27367459107465, 4.640393200077345, 2.386411077932438, 0.5550197984423056], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.8011211593148664, 0.6477903213197327, 3.843646125828579, 0.6184781538385243, 0.6208021383321433, 2.8555723260191157, 0.5863401177493308, 2.898794261275204, 0.6670248531834813, 2.571547596126062, 0.7740863462693214, 2.7557167015154054, 3.5813657350158477, 4.652300986043143, 2.4082986362590817, 3.0589357068356655, 0.5652169711435072, 2.8970140385921535, 3.7514162961229385, 2.2446818029851645], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.9953042661250455, 0.6106381641076838, 2.3157436621008105, 0.548858682849119, 2.1015806185613974, 2.4180652997669556, 2.8220017315726755, 0.6449607823838671, 2.3004860821730033, 0.5744556782609737, 2.5849629372227882, 0.4775041720151005, 0.6464812140919002, 2.8594501189802872, 0.634714227243585, 3.013623667678513, 0.5797299928200865, 0.5498321214180105, 0.7188864877841165, 2.848143664130929], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8536057483716883, 0.7940153834476833, 0.8408023880508473, 0.8021042716176339, 0.9446142560796879, 0.8117091310035226, 0.8281455307670448, 0.8144350579989142, 0.8774951260929015, 0.7882139153963649, 0.8756776306488133, 0.7671321377235709, 0.8872950382733553, 0.7780777136849406, 0.9361458399261262, 0.7545713892188318, 0.8788462391265818, 0.8130097594244071, 0.8654627651144444, 0.8285368711157823], \'SVC(C=1, random_state=13)\': [1.1270751148849465, 1.0704151285304595, 1.0800656396027408, 1.047884337619527, 1.138244467805835, 1.0597858654425623, 1.1136492917882408, 1.035288511035513, 1.1951357933708657, 1.0347517528431547, 1.124929571161903, 1.0698573470289943, 1.126645619981675, 1.0359748374184772, 1.1623202429302588, 1.0130243525481863, 1.1510824486974607, 1.0237710017471464, 1.1502028786400003, 1.0347780570196388], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8779450057894905, 0.8384731860882925, 0.8659182549705661, 0.849849492520418, 0.9580829126923679, 0.8649392829607035, 0.8766531906200122, 0.8279235901651308, 0.902104932703315, 0.8017229095444675, 0.9240943286020497, 0.7920449855853591, 0.9011134726566747, 0.8041043036226432, 0.9963282420417513, 0.7682956290712528, 0.9027071464890423, 0.8387956467642517, 0.8899453404243297, 0.8660009030317191], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.220469471634622, 8.90490260201718, 8.382244974213293, 12.297246450404678, 10.896918466477281, 8.90490260201718, 11.735142963898612, 8.90490260201718, 10.058693969055952, 7.208730677823432, 10.896918466477281, 8.90490260201718, 11.316030715187946, 8.904902602017179, 9.639581720345287, 8.480859620968744, 10.058693969055952, 10.177031545162492, 10.477806217766616, 10.60107452621093], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [5.664414778646546, 2.9566268419976995, 4.835619702344012, 5.3913300641340935, 6.529557969242208, 4.482776898079909, 6.131280132964428, 4.937439757780633, 5.761896560056275, 5.292088308812027, 5.734371866868698, 3.6476157864379544, 4.12514081988409, 2.8593838988732254, 3.2741417609666197, 4.075043262456411, 5.306436197052483, 5.790295897619957, 4.090162275773014, 3.7054710487725067], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [3.7136160270952745, 2.6004487670555347, 3.3243887210980176, 3.8481136920634365, 4.598422960731339, 2.93043205915066, 4.210600767057875, 2.5390761390848584, 4.613394413105484, 2.9287673584180283, 4.198025106351303, 2.117310988194218, 2.615699630292426, 2.0967117237858908, 2.5688414205123733, 2.1576040929975058, 3.7567857478014526, 3.417356814579714, 2.9902594658662602, 2.955577576845991], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9970491844277667, 1.6135756859422667, 3.252640431613678, 2.012384307062857, 1.5163215644524113, 2.056978395920703, 2.0292346075621874, 2.871409584045054, 2.7592379330708394, 1.9031632765474154, 2.403603820642901, 1.6306465196432975, 2.504353397384172, 1.9785652082284093, 2.357802920797729, 2.4561287188290803, 2.8106097667796712, 2.4607500598944285, 1.6394969167613813, 3.2215928261599642], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8746121671891799, 0.821312484441898, 1.2740486418088404, 0.8615769008973208, 0.8465034528680555, 0.9063159373994834, 0.8774048475761403, 1.2293956855929624, 1.209954630886059, 1.1913049214888283, 0.9090137535328043, 0.8639439755567736, 0.9372524485632162, 0.8346641423984155, 1.2322192438335595, 0.9121820359969655, 0.8626001084649825, 0.9274915769188505, 0.9675993691464556, 0.8520778314993954], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.848124611203789, 0.830849857101178, 1.2574894151988603, 0.8430976902000973, 0.8563871439492173, 0.8772312265132021, 0.896306545290467, 0.8553722491398091, 0.839639785881199, 0.7980351638370646, 0.8867929824252528, 0.846772705860414, 0.88914001332345, 0.8197473275394525, 0.8348859019576927, 0.8754323433149382, 0.8683670143106946, 0.8908400919801615, 0.9076899601576777, 0.8447301241706856], \'MLPClassifier(max_iter=2000, random_state=13)\': [2.1010226601618216, 4.025193330451532, 5.101655395265867, 2.735076297782362, 2.5978252942538123, 4.062590009143924, 0.6557084018021072, 4.939606176553077, 2.752989932517112, 4.174209650688717, 4.594990645575637, 3.2306782605666506, 6.56600250791628, 2.7179714394116647, 4.732128849387856, 3.5988059825175127, 4.2759008908108544, 4.228778159280603, 2.430639333366926, 3.3242613353791985], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.6041513946750424, 3.034840904424633, 3.7755705934027506, 2.8001261279556684, 2.7425599384891943, 3.1006857684641096, 3.6409077177531484, 2.6891061719404195, 2.533615419219826, 1.789698331383565, 1.9370390914002467, 2.449160062115682, 0.6546144183616474, 2.773953412240717, 2.4849795098119647, 0.5240691122100491, 3.7657207063878064, 2.5338848274423946, 0.6552766291881482, 0.5261562634773863], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.6107070934707869, 0.5202656605817318, 2.776265982667481, 0.5032742612964329, 0.5015249091425988, 0.5746564786597338, 2.394439574103096, 0.5830131805404161, 0.6305290117805018, 0.524762028251509, 0.6233170882728611, 0.4782867827229653, 0.6630262414155212, 2.4708671465129775, 2.22321537186094, 0.6861116799171597, 2.5018920728799525, 2.8424233441409688, 0.5481151398411442, 1.8216129914276438], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8628904841939838, 0.8391565831875696, 0.8379493260271892, 0.743454331768305, 0.8891393124293793, 0.8100081812329756, 0.8772269943241976, 0.8039578694917277, 0.8527739668361997, 0.7511991026943919, 0.8981204545059359, 0.8526385470314772, 0.9113404574530743, 0.9056648350126435, 0.8368646819564686, 0.8269925899330969, 0.8645502718387035, 0.7512303156156241, 0.8744650531268503, 0.7531825936011836], \'SVC(C=1, random_state=13)\': [1.0926775920273377, 1.0601888604212888, 1.1036054623784128, 1.0464980844110894, 1.1257539943061041, 1.0361238354406574, 1.1276123785646002, 1.0485170513325983, 1.1372774003364192, 1.0227648628827068, 1.1149455291754735, 1.0249369944081976, 1.128087237525525, 1.026214445027499, 1.0689864677272538, 1.0698841950712368, 1.079501104225123, 1.0700294843423446, 1.1035767141044257, 1.047229039315916], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8886060135284131, 0.8413801959999536, 0.8631036631910665, 0.7688239343868685, 0.9024502328796854, 0.8367791906995844, 0.8790454951517561, 0.8535249983211768, 0.9007949078290989, 0.777008569533927, 0.9119644984031446, 0.8655910147732044, 0.9482896903942153, 0.9187537073554087, 0.8852441806888971, 0.8409809393823542, 0.9012669547983264, 0.8245956589012748, 0.8990982834591585, 0.7907820639144103], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [7.963132725502628, 9.328945583065618, 11.316030715187946, 8.056816639920306, 10.477806217766616, 8.480859620968744, 10.058693969055952, 8.904902602017183, 7.963132725502629, 10.177031545162492, 11.316030715187946, 12.297246450404678, 9.639581720345287, 11.873203469356243, 11.73514296389861, 8.480859620968744, 10.058693969055952, 10.177031545162492, 8.801357222923958, 9.328945583065618], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [3.654930325188862, 5.766445008907712, 6.941216367029373, 2.8729218787533095, 5.745776858182788, 4.9149745518408166, 4.505929384106332, 4.881583307643673, 3.634095912755978, 5.779369859362631, 3.673789167426451, 6.237417214033377, 5.271615223096969, 4.955747915403166, 4.51064409466573, 5.726284774770526, 5.718858165008456, 4.546015467582076, 4.871967816637138, 5.732440635285404], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.9558587133830234, 2.9974025117158067, 4.220703763321125, 2.601152950270043, 4.19815643200966, 3.369613220278465, 3.793464088542506, 2.9336836834545785, 2.931204486217906, 3.842159072347416, 2.585634697530316, 2.6355465288620694, 3.366016215329781, 2.620142607450496, 2.5880304891978883, 4.590266686059546, 4.595905141049945, 2.1929163722308957, 4.146727959577171, 3.008036255384931], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13), MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.0137700423623444, 2.456175744184838, 2.820470345778297, 2.0103805939254378, 3.6429559140423247, 1.7108124649353953, 1.208648674055511, 2.43733271212466, 3.3771770758082513, 2.473724625088105, 2.398628644607838, 2.0427740971283517, 2.3821634081967726, 1.6691336773596794, 3.6015145023146644, 1.614128820922848, 2.0494990343936252, 2.4713860151203795, 2.021144362398991, 1.9983136643019541], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.336707014688057, 0.9166688011040682, 1.2414045320661218, 1.2116046136799932, 1.3270862876010658, 1.2667710635877205, 0.8857942417657048, 1.2673776703931523, 0.9365239738849169, 0.8845349323686831, 1.2980074024510424, 0.8943074692649418, 1.277478193578747, 1.2386812942242003, 0.8661271941390624, 0.8347810090810707, 1.2850695348289076, 1.2325459669246384, 1.281243743069293, 1.2619951275652328], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.9274834886712925, 0.8845071312781246, 0.8744930201394737, 1.2042014129937124, 1.2653623096006066, 0.8755766773597388, 0.8921787055259662, 0.8644310230354936, 0.9390429592706334, 0.8880492998404415, 0.8721496701088671, 0.8666924500626857, 0.8889194615185854, 0.8619811667466705, 0.8910195817068769, 0.7945046523217815, 0.8937389384789851, 0.8557989005635905, 1.2484586926865284, 0.8866663771985922], \'MLPClassifier(max_iter=2000, random_state=13)\': [0.6806748139933017, 0.6263679079067863, 0.5232447942727775, 0.5780669992412883, 2.691395241052382, 0.6820043106961956, 2.369312763537998, 0.5599910532113852, 3.6103056416071735, 2.9871636413288694, 3.597066926641293, 2.1155939733185165, 2.7485472494297185, 0.5916315425794041, 2.023824122343913, 3.4436629652167907, 2.5681813795641935, 1.6293527615683987, 2.4956438243868493, 2.2969121271967197], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.5339461481183335, 2.595098821398311, 0.5610744119126074, 2.759851844769874, 2.23682130022951, 1.9956035352102564, 2.755440783617696, 2.815998421104718, 2.322836066279513, 2.651530219930114, 2.3295426245317237, 2.4398106859488617, 2.245812526655441, 2.8174766795367816, 2.6251594063030312, 2.3640088326424737, 2.787026185996269, 3.686746176509636, 0.6288853319684098, 2.150824875684419], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.6530201776868012, 0.6199263566852907, 4.135446197410429, 2.3805059580164696, 0.5946270356803048, 2.4619185844060407, 0.5357788560860627, 2.570938339612388, 0.6532307359875664, 1.7064659217381286, 3.292551699065491, 1.9673527914519033, 0.5561764100147598, 0.6279575346996326, 0.5817247338392257, 0.7896254267078971, 3.9623188895949766, 2.6812559575483084, 1.5631770401041447, 3.2928557967849748], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8607062775939263, 0.8293527939187348, 0.8520076294279817, 0.8129144344636203, 0.9517644772351727, 0.7891603017098409, 0.8389057202816219, 0.779701793961366, 0.8547615046774694, 0.7771879317886017, 0.837149133919509, 0.7517571395259621, 0.8790743505686998, 0.7900836083628381, 0.8653615271064123, 0.7770882048403626, 0.8637065418326307, 0.8132866471437159, 0.8508152609575838, 0.7531569801545926], \'SVC(C=1, random_state=13)\': [1.1360411243387334, 1.0125106789603504, 1.0664622275978337, 1.0814215460629477, 1.080598553642021, 1.1061143030025942, 1.137419495596731, 1.044224684279257, 1.1023771060605012, 1.0687568151022377, 1.1370704865079069, 1.0222771392305339, 1.126752032983356, 1.0588036943428363, 1.159725090525904, 0.9988642013496527, 1.1013928266219775, 1.1049047831314143, 1.125809299392401, 1.0237693968050654], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8861328996864938, 0.8428747825300823, 0.8657498452915645, 0.8737216338836402, 0.9647666616522841, 0.8268646180040924, 0.8644199172361586, 0.8051648611370009, 0.8792794301541589, 0.8029818289169075, 0.8279121202238378, 0.7892125754471012, 0.8921080821487335, 0.80391211874469, 0.8780848438861754, 0.767676632253331, 0.877171912480038, 0.8506984487324223, 0.88743723476035, 0.7908632723059921], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.639581720345289, 8.90490260201718, 9.639581720345287, 10.177031545162492, 10.896918466477281, 10.177031545162492, 12.992479710030608, 10.60107452621093, 7.963132725502629, 9.752988564114057, 9.639581720345289, 8.90490260201718, 10.058693969055952, 11.025117507259367, 11.73514296389861, 9.752988564114055, 10.896918466477281, 12.29724645040468, 11.73514296389861, 9.752988564114055], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.956124068876372, 4.083197935168882, 3.675764737621747, 5.384561074194052, 7.358353045544742, 4.062118412001492, 6.549022811493041, 5.773213998847753, 4.866489535908935, 5.80860405524249, 4.89006308870592, 5.761674831165262, 6.894832831604206, 8.250848820666189, 6.571832794121221, 4.513396776732196, 4.87865809739183, 7.430611371676745, 6.120481141663582, 4.070273084713963], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [5.4660163958771815, 4.158549291057701, 2.176028742714195, 3.444871216222184, 5.417115040770624, 3.361257306767137, 5.020206774674895, 3.4322253837274688, 3.776539485866205, 3.841678813588355, 3.358521033772274, 3.4269749472259585, 5.816839320006204, 4.66986969449141, 5.069736549687837, 1.763330660092747, 3.400506962837367, 5.101587089493256, 5.410370307133321, 3.7674591123241052], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13), MLPClassifier(max_iter=2000, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.923321418133782, 1.5830935788959088, 2.005676835124909, 2.1660057759601123, 2.432425582918879, 2.0446617739511224, 2.797620914394025, 1.5919216830172986, 2.868271811812724, 3.413320623492055, 2.426483564243341, 1.2783308922744592, 4.02674142599323, 2.467323495340784, 2.862269720069233, 1.6706886689089706, 1.6046703226205243, 2.0302303834941515, 2.42812890799071, 2.0845368259967585], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.2448814340630103, 0.8874639234035964, 1.232094991586328, 0.9110287810436781, 1.276241655738427, 1.2307995740032238, 1.2776351528557472, 0.8523883221063436, 1.3074921496761693, 1.7026226512394755, 0.885322181213056, 0.8287375358928672, 0.9400996546404197, 0.8460091803244207, 0.8612882918116429, 1.2569696266319303, 1.2521281933609305, 0.8475337637037509, 1.2882617341065836, 0.8867513540080625], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8627467841624131, 0.8717142654696048, 0.8714629191971838, 0.9153289826586356, 0.9238214402042384, 0.8502821412148214, 0.8704529625404885, 0.8229350980418544, 0.9098363123836569, 0.9323603798660646, 0.8912667913967287, 0.8484161793498873, 0.9107345870412771, 0.838674507644832, 0.8720455254363868, 1.2224086749165213, 1.2478120511223203, 0.8350205080858234, 0.9118362678007955, 0.8845941020021117], \'MLPClassifier(max_iter=2000, random_state=13)\': [3.8859171816079114, 2.4911695296436296, 2.4573065313197784, 4.10888457529224, 2.5226993920995913, 1.7374586208403096, 2.347276511976145, 3.0271222768577055, 2.49697658561752, 4.259517772515293, 0.7008111277510864, 1.9914862152115176, 2.0416404814378595, 3.7444009846940864, 3.679244631602545, 2.4282112975892605, 3.3306353935909443, 2.185823360009586, 2.8722467137977987, 2.7720426273753516], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.8784808602464405, 3.652442882636654, 2.414295456519647, 2.5446784004946617, 3.1737280832904196, 2.8725869215031037, 4.911538830148408, 4.188815307932042, 2.724484146580634, 2.651367534729905, 4.602739110584875, 1.984505104387195, 2.972976985331631, 3.059982252612479, 3.6656916332262472, 2.1697154369474583, 0.5450292647469704, 2.623056687611636, 0.7492251798519469, 2.2981219682519107], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [3.091507781863673, 0.5446362230976317, 0.5655935636886622, 0.5518877728745534, 2.8828433946603913, 3.9596293182430546, 0.5433121142851423, 2.218594801523848, 2.5495030899126148, 0.5643766472289381, 2.2220795976686016, 0.6463774756136758, 0.5711254687546714, 0.5984431446155191, 0.8399394293057193, 3.042407135563726, 0.6248247793367256, 0.5750337033697407, 0.6822132307181175, 3.6985681291008405], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8649854883575002, 0.7663138336871501, 0.79401496939446, 0.8168860774884295, 0.8762374654181798, 0.792672985350602, 0.8639588606141665, 0.7196014233766738, 0.9383777670765467, 0.8352709659235908, 0.8624973469191406, 0.8512150573616236, 0.8532716298281291, 0.7659522885994116, 0.8507049626768898, 0.803066180089058, 0.8406506515246747, 0.7674706757246004, 0.9254312214246103, 0.7909437926294417], \'SVC(C=1, random_state=13)\': [1.1145110669244493, 1.0240034800094193, 1.0800183236211574, 1.1059148354868271, 1.114292450460384, 1.0119123358621784, 1.091060673462963, 0.9875975739241802, 1.2097559249653522, 1.1424805091969017, 1.0914154346105602, 1.0476012872745535, 1.102391341676892, 1.0702827326108095, 1.067631486557756, 1.0587131651543054, 1.0807574862603984, 1.046911808438411, 1.1056683668042253, 1.068489425738346], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9017800973323225, 0.8035845648900131, 0.8424086164023881, 0.8424380526152511, 0.8894935268464805, 0.7944190167871693, 0.8771775558775986, 0.7808594852494181, 0.9988676086906559, 0.8719066967934455, 0.8994351638539928, 0.8650688714459694, 0.8895041492639847, 0.7917740488379879, 0.8760182587078148, 0.8522878500247565, 0.8771039310209795, 0.8036852339439132, 0.9375559464350928, 0.8405225431801925], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [10.896918466477281, 8.480859620968744, 12.57336746131994, 10.177031545162492, 10.896918466477281, 7.63277365887187, 8.382244974213291, 10.177031545162492, 11.316030715187946, 11.025117507259367, 9.220469471634624, 10.60107452621093, 7.963132725502628, 6.784687696774995, 8.382244974213293, 10.60107452621093, 9.639581720345287, 8.056816639920306, 8.801357222923958, 13.99341837459843], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [3.6596450357482584, 3.685004655030282, 4.972794738424214, 4.926513719523307, 4.951354325978084, 3.673465487347791, 5.239218249194433, 4.142438880275862, 6.164889106893452, 4.580792394551647, 2.8563990824380068, 5.347172205601723, 4.461521418876461, 2.8649266299629375, 2.787205564384661, 6.222493551380864, 4.051232591271347, 3.6673096268329144, 4.824214711029921, 9.12955466141535], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.937330097593361, 3.359592606034505, 3.00761741226344, 3.3226156260684827, 4.991986086449721, 2.129197543969668, 4.532452555041519, 2.5868881035188633, 4.650678753859782, 2.6293128911858474, 2.148070705805738, 3.4286396479585894, 2.973953985451806, 2.1425893765556507, 2.128330089989587, 3.8019437447054742, 2.9507237813513485, 2.91275030758129, 3.287248828250679, 5.121001911928013], \'removed_models\': "[[RandomForestClassifier(n_jobs=-1, random_state=13), RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)], [SVC(C=1, kernel=\'linear\', random_state=13), SVC(C=1, kernel=\'poly\', random_state=13)]]"}'}</t>
+  </si>
+  <si>
+    <t>{0: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9447727669874642, 2.8019991880170134, 1.6458236147674554, 1.546234683801399, 2.4114800788797277, 1.5862320192681403, 2.3923432772357724, 2.393026016915189, 2.0791362436201997, 2.046818746879295, 2.5800075972130534, 2.0180488437475006, 2.8834421649764375, 1.5753822490055667, 2.0849653751081907, 2.416341245824442, 2.3366857050063246, 2.4802537245617033, 1.2468230666848195, 2.4452083668769267], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.9216185665281814, 1.6400885383327464, 0.9124798945245478, 0.8148475885275268, 0.8921122680772945, 0.8215033526867803, 1.2486139599804753, 0.8622413083052717, 0.856065248270181, 1.2543180212300291, 1.3002760634976653, 1.2780742615017548, 1.2988354551569303, 1.237884720400324, 0.9018064245023566, 0.9111435324499801, 1.200963169741228, 1.2381554711622547, 0.8768566187998464, 0.8632538456240632], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.9291839306401382, 1.6227141527911777, 0.8818797901483901, 0.8291400339495646, 0.8703516058203228, 0.8304798346978411, 0.8406733995535693, 0.8451058670630862, 0.8729350179182653, 0.8628147670219878, 1.2857613740113505, 0.8736633549249033, 1.2633918505499842, 0.8855071843852161, 0.8886872461444426, 0.8588699465422046, 0.8354950012306536, 0.858157058275449, 0.8986754409707841, 0.8533209984299027], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.2341725147731233, 2.240505741794485, 2.2724576777645447, 4.4580096468753, 3.6616919494426834, 2.6932937765647726, 2.678091156807596, 4.575334491226991, 2.2868969942545916, 1.6493523116809676, 3.901641229560317, 0.5740182725204063, 0.610669725553231, 4.680062016438082, 0.6651768927194867, 5.30775012758612, 2.7673235603888915, 3.3728728756693633, 0.5904033614379076, 0.5992450621165876], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [2.75871661563757, 2.640061686294103, 2.8446195086208035, 0.635065571256506, 4.186697995182309, 0.4739601907566424, 0.5819830661049413, 0.5799994800247998, 3.8100869562272224, 2.641985620287596, 3.481178891169509, 2.3970415615505827, 3.903225534427142, 2.2647203019962774, 3.4482210882898605, 2.554344031709773, 2.4348052644193716, 1.99542081795396, 2.9172492917487056, 2.200485088284743], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.7945314949122055, 3.4018899899138213, 0.6136137856582025, 2.301085862198831, 0.5097745291109792, 2.137822273635953, 0.49444190698412244, 0.5395169119538139, 0.5489289959020404, 3.293271532828209, 3.251648927549524, 0.550219540405023, 2.689148293586088, 0.5292784202302115, 0.6284554290592425, 3.0006078797842104, 0.6254097435811034, 0.5437023815862057, 0.5217696925411303, 2.161240938424042], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.9112674278110563, 0.9408668515755663, 0.826895255531877, 0.7177162636869742, 0.8047028685079268, 0.7750599402342997, 0.8268239536798073, 0.7889847287564593, 0.842735118434121, 0.7018609127523037, 0.8143220596839099, 0.8152819065565253, 0.8260321336129692, 0.7314143442944568, 0.8136526107180247, 0.7663517344958745, 0.8403989265912932, 0.7636647837986532, 0.8020069147318423, 0.7427683933231543], \'SVC(C=1, random_state=13)\': [1.1171986522337094, 1.143277602854134, 1.148062513252707, 1.031392354680479, 1.0784274284575663, 1.0213250995254632, 1.0907405600669178, 1.0213231799430311, 1.100190194156102, 1.0099927457695217, 1.0908201516488356, 1.0692788688746808, 1.101366927716333, 1.0210313936659425, 1.1466307015718091, 1.0789114004897895, 1.1245827634031087, 1.0336193183941513, 1.0777612118297095, 1.0333905257517086], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9364724275918026, 0.9432191276782146, 0.8284826524264565, 0.7549054769820758, 0.8297112930007314, 0.8008662237008366, 0.8403227603103225, 0.7792748413515256, 0.8439371683691516, 0.775513865917793, 0.8398726570168208, 0.8287383659096759, 0.8397570028556799, 0.7803510674792085, 0.8505900613132106, 0.780170821358957, 0.8535496745986705, 0.7776515113420084, 0.8145012620258045, 0.7682934094718228], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [10.896918466477281, 14.41746135564687, 12.154255212609277, 8.056816639920306, 9.220469471634622, 11.025117507259369, 10.058693969055952, 8.480859620968744, 9.639581720345289, 9.752988564114055, 10.896918466477281, 8.480859620968745, 10.058693969055952, 9.752988564114057, 11.316030715187944, 8.90490260201718, 11.73514296389861, 10.177031545162492, 9.220469471634622, 10.60107452621093], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [5.757945419665684, 5.8235277178950025, 7.3953071598511135, 3.6408467964979123, 4.091531845955065, 5.819530093499816, 4.507298954288384, 3.694545010515181, 5.737717007246045, 5.372408777086395, 6.0929564484760075, 3.73531837407753, 5.299139916284545, 3.3242002434840128, 6.150138975202017, 4.906819879128347, 6.12656542240503, 4.940824252750654, 5.292449635529854, 6.17756313950123], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [4.215700156947808, 3.8371325603013533, 4.640842233517311, 2.921865497811883, 3.3570070156832625, 3.818454330929273, 4.252667393502782, 2.5576633146675953, 3.839902076850281, 3.383631458917611, 4.991312511305266, 3.0152987807120333, 3.347012925185231, 2.621528290222923, 4.210036097678636, 3.3568212404896487, 3.360076382495292, 2.5884844341187394, 3.798377699891472, 3.8326964940238653]}', 1: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.4507013173064185, 2.848688521627796, 2.77049847647797, 1.2321636342994973, 2.8346193214086424, 2.472201170709748, 2.468340353491126, 2.020406109109224, 2.470742237614099, 1.6622660433074683, 3.6317367012692015, 2.3629277360725496, 2.471680177646263, 2.055310220439726, 2.490304576952541, 1.3700630363312163, 2.395363035117345, 1.2343791754807727, 3.295544066658845, 2.371612860109013], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.2876800271365385, 1.2658538198088465, 1.6155460661769019, 0.8891281084268284, 0.8604466336650688, 0.8327744514219056, 1.269085135073887, 0.8517683070569572, 1.2969057726816378, 0.8613626866463661, 0.8752463649208391, 1.2429679149866937, 0.901620510317477, 0.8551193634156518, 1.3015725191346916, 0.9164283659050546, 1.6605278826344883, 0.8547465705010743, 1.2760501461286906, 0.8887450535093594], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [1.2943204054986868, 0.8560923204819865, 0.8769678825170599, 0.8726498664365719, 0.8551552819886147, 0.8409595520476546, 1.2445651196027112, 0.870702528986893, 0.8886979906500823, 0.8379244067396873, 0.8784198832601995, 0.8702115083841507, 0.8779966450953229, 0.8809705681830606, 0.90640540750931, 0.8948271909521106, 0.9129244479177803, 0.8466118610370713, 0.8940090259098938, 0.8508323639694254], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.8734307261953447, 3.991175512584563, 0.6146523400175986, 1.6550914748949117, 2.4455740897973866, 3.0081009194066177, 3.7752779974958157, 1.629597475818563, 0.7159939869784093, 3.1536069828688795, 6.410205981459273, 3.8181415403534817, 3.5463724504434184, 0.5280118082446285, 3.4573909405148697, 2.3678393725002733, 2.27367459107465, 4.640393200077345, 2.386411077932438, 0.5550197984423056], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.8011211593148664, 0.6477903213197327, 3.843646125828579, 0.6184781538385243, 0.6208021383321433, 2.8555723260191157, 0.5863401177493308, 2.898794261275204, 0.6670248531834813, 2.571547596126062, 0.7740863462693214, 2.7557167015154054, 3.5813657350158477, 4.652300986043143, 2.4082986362590817, 3.0589357068356655, 0.5652169711435072, 2.8970140385921535, 3.7514162961229385, 2.2446818029851645], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [2.9953042661250455, 0.6106381641076838, 2.3157436621008105, 0.548858682849119, 2.1015806185613974, 2.4180652997669556, 2.8220017315726755, 0.6449607823838671, 2.3004860821730033, 0.5744556782609737, 2.5849629372227882, 0.4775041720151005, 0.6464812140919002, 2.8594501189802872, 0.634714227243585, 3.013623667678513, 0.5797299928200865, 0.5498321214180105, 0.7188864877841165, 2.848143664130929], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8536057483716883, 0.7940153834476833, 0.8408023880508473, 0.8021042716176339, 0.9446142560796879, 0.8117091310035226, 0.8281455307670448, 0.8144350579989142, 0.8774951260929015, 0.7882139153963649, 0.8756776306488133, 0.7671321377235709, 0.8872950382733553, 0.7780777136849406, 0.9361458399261262, 0.7545713892188318, 0.8788462391265818, 0.8130097594244071, 0.8654627651144444, 0.8285368711157823], \'SVC(C=1, random_state=13)\': [1.1270751148849465, 1.0704151285304595, 1.0800656396027408, 1.047884337619527, 1.138244467805835, 1.0597858654425623, 1.1136492917882408, 1.035288511035513, 1.1951357933708657, 1.0347517528431547, 1.124929571161903, 1.0698573470289943, 1.126645619981675, 1.0359748374184772, 1.1623202429302588, 1.0130243525481863, 1.1510824486974607, 1.0237710017471464, 1.1502028786400003, 1.0347780570196388], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8779450057894905, 0.8384731860882925, 0.8659182549705661, 0.849849492520418, 0.9580829126923679, 0.8649392829607035, 0.8766531906200122, 0.8279235901651308, 0.902104932703315, 0.8017229095444675, 0.9240943286020497, 0.7920449855853591, 0.9011134726566747, 0.8041043036226432, 0.9963282420417513, 0.7682956290712528, 0.9027071464890423, 0.8387956467642517, 0.8899453404243297, 0.8660009030317191], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.220469471634622, 8.90490260201718, 8.382244974213293, 12.297246450404678, 10.896918466477281, 8.90490260201718, 11.735142963898612, 8.90490260201718, 10.058693969055952, 7.208730677823432, 10.896918466477281, 8.90490260201718, 11.316030715187946, 8.904902602017179, 9.639581720345287, 8.480859620968744, 10.058693969055952, 10.177031545162492, 10.477806217766616, 10.60107452621093], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [5.664414778646546, 2.9566268419976995, 4.835619702344012, 5.3913300641340935, 6.529557969242208, 4.482776898079909, 6.131280132964428, 4.937439757780633, 5.761896560056275, 5.292088308812027, 5.734371866868698, 3.6476157864379544, 4.12514081988409, 2.8593838988732254, 3.2741417609666197, 4.075043262456411, 5.306436197052483, 5.790295897619957, 4.090162275773014, 3.7054710487725067], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [3.7136160270952745, 2.6004487670555347, 3.3243887210980176, 3.8481136920634365, 4.598422960731339, 2.93043205915066, 4.210600767057875, 2.5390761390848584, 4.613394413105484, 2.9287673584180283, 4.198025106351303, 2.117310988194218, 2.615699630292426, 2.0967117237858908, 2.5688414205123733, 2.1576040929975058, 3.7567857478014526, 3.417356814579714, 2.9902594658662602, 2.955577576845991]}', 2: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.9970491844277667, 1.6135756859422667, 3.252640431613678, 2.012384307062857, 1.5163215644524113, 2.056978395920703, 2.0292346075621874, 2.871409584045054, 2.7592379330708394, 1.9031632765474154, 2.403603820642901, 1.6306465196432975, 2.504353397384172, 1.9785652082284093, 2.357802920797729, 2.4561287188290803, 2.8106097667796712, 2.4607500598944285, 1.6394969167613813, 3.2215928261599642], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [0.8746121671891799, 0.821312484441898, 1.2740486418088404, 0.8615769008973208, 0.8465034528680555, 0.9063159373994834, 0.8774048475761403, 1.2293956855929624, 1.209954630886059, 1.1913049214888283, 0.9090137535328043, 0.8639439755567736, 0.9372524485632162, 0.8346641423984155, 1.2322192438335595, 0.9121820359969655, 0.8626001084649825, 0.9274915769188505, 0.9675993691464556, 0.8520778314993954], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.848124611203789, 0.830849857101178, 1.2574894151988603, 0.8430976902000973, 0.8563871439492173, 0.8772312265132021, 0.896306545290467, 0.8553722491398091, 0.839639785881199, 0.7980351638370646, 0.8867929824252528, 0.846772705860414, 0.88914001332345, 0.8197473275394525, 0.8348859019576927, 0.8754323433149382, 0.8683670143106946, 0.8908400919801615, 0.9076899601576777, 0.8447301241706856], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [2.1010226601618216, 4.025193330451532, 5.101655395265867, 2.735076297782362, 2.5978252942538123, 4.062590009143924, 0.6557084018021072, 4.939606176553077, 2.752989932517112, 4.174209650688717, 4.594990645575637, 3.2306782605666506, 6.56600250791628, 2.7179714394116647, 4.732128849387856, 3.5988059825175127, 4.2759008908108544, 4.228778159280603, 2.430639333366926, 3.3242613353791985], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.6041513946750424, 3.034840904424633, 3.7755705934027506, 2.8001261279556684, 2.7425599384891943, 3.1006857684641096, 3.6409077177531484, 2.6891061719404195, 2.533615419219826, 1.789698331383565, 1.9370390914002467, 2.449160062115682, 0.6546144183616474, 2.773953412240717, 2.4849795098119647, 0.5240691122100491, 3.7657207063878064, 2.5338848274423946, 0.6552766291881482, 0.5261562634773863], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.6107070934707869, 0.5202656605817318, 2.776265982667481, 0.5032742612964329, 0.5015249091425988, 0.5746564786597338, 2.394439574103096, 0.5830131805404161, 0.6305290117805018, 0.524762028251509, 0.6233170882728611, 0.4782867827229653, 0.6630262414155212, 2.4708671465129775, 2.22321537186094, 0.6861116799171597, 2.5018920728799525, 2.8424233441409688, 0.5481151398411442, 1.8216129914276438], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8628904841939838, 0.8391565831875696, 0.8379493260271892, 0.743454331768305, 0.8891393124293793, 0.8100081812329756, 0.8772269943241976, 0.8039578694917277, 0.8527739668361997, 0.7511991026943919, 0.8981204545059359, 0.8526385470314772, 0.9113404574530743, 0.9056648350126435, 0.8368646819564686, 0.8269925899330969, 0.8645502718387035, 0.7512303156156241, 0.8744650531268503, 0.7531825936011836], \'SVC(C=1, random_state=13)\': [1.0926775920273377, 1.0601888604212888, 1.1036054623784128, 1.0464980844110894, 1.1257539943061041, 1.0361238354406574, 1.1276123785646002, 1.0485170513325983, 1.1372774003364192, 1.0227648628827068, 1.1149455291754735, 1.0249369944081976, 1.128087237525525, 1.026214445027499, 1.0689864677272538, 1.0698841950712368, 1.079501104225123, 1.0700294843423446, 1.1035767141044257, 1.047229039315916], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8886060135284131, 0.8413801959999536, 0.8631036631910665, 0.7688239343868685, 0.9024502328796854, 0.8367791906995844, 0.8790454951517561, 0.8535249983211768, 0.9007949078290989, 0.777008569533927, 0.9119644984031446, 0.8655910147732044, 0.9482896903942153, 0.9187537073554087, 0.8852441806888971, 0.8409809393823542, 0.9012669547983264, 0.8245956589012748, 0.8990982834591585, 0.7907820639144103], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [7.963132725502628, 9.328945583065618, 11.316030715187946, 8.056816639920306, 10.477806217766616, 8.480859620968744, 10.058693969055952, 8.904902602017183, 7.963132725502629, 10.177031545162492, 11.316030715187946, 12.297246450404678, 9.639581720345287, 11.873203469356243, 11.73514296389861, 8.480859620968744, 10.058693969055952, 10.177031545162492, 8.801357222923958, 9.328945583065618], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [3.654930325188862, 5.766445008907712, 6.941216367029373, 2.8729218787533095, 5.745776858182788, 4.9149745518408166, 4.505929384106332, 4.881583307643673, 3.634095912755978, 5.779369859362631, 3.673789167426451, 6.237417214033377, 5.271615223096969, 4.955747915403166, 4.51064409466573, 5.726284774770526, 5.718858165008456, 4.546015467582076, 4.871967816637138, 5.732440635285404], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.9558587133830234, 2.9974025117158067, 4.220703763321125, 2.601152950270043, 4.19815643200966, 3.369613220278465, 3.793464088542506, 2.9336836834545785, 2.931204486217906, 3.842159072347416, 2.585634697530316, 2.6355465288620694, 3.366016215329781, 2.620142607450496, 2.5880304891978883, 4.590266686059546, 4.595905141049945, 2.1929163722308957, 4.146727959577171, 3.008036255384931]}', 3: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [2.0137700423623444, 2.456175744184838, 2.820470345778297, 2.0103805939254378, 3.6429559140423247, 1.7108124649353953, 1.208648674055511, 2.43733271212466, 3.3771770758082513, 2.473724625088105, 2.398628644607838, 2.0427740971283517, 2.3821634081967726, 1.6691336773596794, 3.6015145023146644, 1.614128820922848, 2.0494990343936252, 2.4713860151203795, 2.021144362398991, 1.9983136643019541], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.336707014688057, 0.9166688011040682, 1.2414045320661218, 1.2116046136799932, 1.3270862876010658, 1.2667710635877205, 0.8857942417657048, 1.2673776703931523, 0.9365239738849169, 0.8845349323686831, 1.2980074024510424, 0.8943074692649418, 1.277478193578747, 1.2386812942242003, 0.8661271941390624, 0.8347810090810707, 1.2850695348289076, 1.2325459669246384, 1.281243743069293, 1.2619951275652328], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.9274834886712925, 0.8845071312781246, 0.8744930201394737, 1.2042014129937124, 1.2653623096006066, 0.8755766773597388, 0.8921787055259662, 0.8644310230354936, 0.9390429592706334, 0.8880492998404415, 0.8721496701088671, 0.8666924500626857, 0.8889194615185854, 0.8619811667466705, 0.8910195817068769, 0.7945046523217815, 0.8937389384789851, 0.8557989005635905, 1.2484586926865284, 0.8866663771985922], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [0.6806748139933017, 0.6263679079067863, 0.5232447942727775, 0.5780669992412883, 2.691395241052382, 0.6820043106961956, 2.369312763537998, 0.5599910532113852, 3.6103056416071735, 2.9871636413288694, 3.597066926641293, 2.1155939733185165, 2.7485472494297185, 0.5916315425794041, 2.023824122343913, 3.4436629652167907, 2.5681813795641935, 1.6293527615683987, 2.4956438243868493, 2.2969121271967197], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [0.5339461481183335, 2.595098821398311, 0.5610744119126074, 2.759851844769874, 2.23682130022951, 1.9956035352102564, 2.755440783617696, 2.815998421104718, 2.322836066279513, 2.651530219930114, 2.3295426245317237, 2.4398106859488617, 2.245812526655441, 2.8174766795367816, 2.6251594063030312, 2.3640088326424737, 2.787026185996269, 3.686746176509636, 0.6288853319684098, 2.150824875684419], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [0.6530201776868012, 0.6199263566852907, 4.135446197410429, 2.3805059580164696, 0.5946270356803048, 2.4619185844060407, 0.5357788560860627, 2.570938339612388, 0.6532307359875664, 1.7064659217381286, 3.292551699065491, 1.9673527914519033, 0.5561764100147598, 0.6279575346996326, 0.5817247338392257, 0.7896254267078971, 3.9623188895949766, 2.6812559575483084, 1.5631770401041447, 3.2928557967849748], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8607062775939263, 0.8293527939187348, 0.8520076294279817, 0.8129144344636203, 0.9517644772351727, 0.7891603017098409, 0.8389057202816219, 0.779701793961366, 0.8547615046774694, 0.7771879317886017, 0.837149133919509, 0.7517571395259621, 0.8790743505686998, 0.7900836083628381, 0.8653615271064123, 0.7770882048403626, 0.8637065418326307, 0.8132866471437159, 0.8508152609575838, 0.7531569801545926], \'SVC(C=1, random_state=13)\': [1.1360411243387334, 1.0125106789603504, 1.0664622275978337, 1.0814215460629477, 1.080598553642021, 1.1061143030025942, 1.137419495596731, 1.044224684279257, 1.1023771060605012, 1.0687568151022377, 1.1370704865079069, 1.0222771392305339, 1.126752032983356, 1.0588036943428363, 1.159725090525904, 0.9988642013496527, 1.1013928266219775, 1.1049047831314143, 1.125809299392401, 1.0237693968050654], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.8861328996864938, 0.8428747825300823, 0.8657498452915645, 0.8737216338836402, 0.9647666616522841, 0.8268646180040924, 0.8644199172361586, 0.8051648611370009, 0.8792794301541589, 0.8029818289169075, 0.8279121202238378, 0.7892125754471012, 0.8921080821487335, 0.80391211874469, 0.8780848438861754, 0.767676632253331, 0.877171912480038, 0.8506984487324223, 0.88743723476035, 0.7908632723059921], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [9.639581720345289, 8.90490260201718, 9.639581720345287, 10.177031545162492, 10.896918466477281, 10.177031545162492, 12.992479710030608, 10.60107452621093, 7.963132725502629, 9.752988564114057, 9.639581720345289, 8.90490260201718, 10.058693969055952, 11.025117507259367, 11.73514296389861, 9.752988564114055, 10.896918466477281, 12.29724645040468, 11.73514296389861, 9.752988564114055], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [6.956124068876372, 4.083197935168882, 3.675764737621747, 5.384561074194052, 7.358353045544742, 4.062118412001492, 6.549022811493041, 5.773213998847753, 4.866489535908935, 5.80860405524249, 4.89006308870592, 5.761674831165262, 6.894832831604206, 8.250848820666189, 6.571832794121221, 4.513396776732196, 4.87865809739183, 7.430611371676745, 6.120481141663582, 4.070273084713963], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [5.4660163958771815, 4.158549291057701, 2.176028742714195, 3.444871216222184, 5.417115040770624, 3.361257306767137, 5.020206774674895, 3.4322253837274688, 3.776539485866205, 3.841678813588355, 3.358521033772274, 3.4269749472259585, 5.816839320006204, 4.66986969449141, 5.069736549687837, 1.763330660092747, 3.400506962837367, 5.101587089493256, 5.410370307133321, 3.7674591123241052]}', 4: '{\'RandomForestClassifier(n_estimators=10, n_jobs=-1, random_state=13)\': [1.923321418133782, 1.5830935788959088, 2.005676835124909, 2.1660057759601123, 2.432425582918879, 2.0446617739511224, 2.797620914394025, 1.5919216830172986, 2.868271811812724, 3.413320623492055, 2.426483564243341, 1.2783308922744592, 4.02674142599323, 2.467323495340784, 2.862269720069233, 1.6706886689089706, 1.6046703226205243, 2.0302303834941515, 2.42812890799071, 2.0845368259967585], \'RandomForestClassifier(n_estimators=50, n_jobs=-1, random_state=13)\': [1.2448814340630103, 0.8874639234035964, 1.232094991586328, 0.9110287810436781, 1.276241655738427, 1.2307995740032238, 1.2776351528557472, 0.8523883221063436, 1.3074921496761693, 1.7026226512394755, 0.885322181213056, 0.8287375358928672, 0.9400996546404197, 0.8460091803244207, 0.8612882918116429, 1.2569696266319303, 1.2521281933609305, 0.8475337637037509, 1.2882617341065836, 0.8867513540080625], \'RandomForestClassifier(n_jobs=-1, random_state=13)\': [0.8627467841624131, 0.8717142654696048, 0.8714629191971838, 0.9153289826586356, 0.9238214402042384, 0.8502821412148214, 0.8704529625404885, 0.8229350980418544, 0.9098363123836569, 0.9323603798660646, 0.8912667913967287, 0.8484161793498873, 0.9107345870412771, 0.838674507644832, 0.8720455254363868, 1.2224086749165213, 1.2478120511223203, 0.8350205080858234, 0.9118362678007955, 0.8845941020021117], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", \'MLPClassifier(max_iter=2000, random_state=13)\': [3.8859171816079114, 2.4911695296436296, 2.4573065313197784, 4.10888457529224, 2.5226993920995913, 1.7374586208403096, 2.347276511976145, 3.0271222768577055, 2.49697658561752, 4.259517772515293, 0.7008111277510864, 1.9914862152115176, 2.0416404814378595, 3.7444009846940864, 3.679244631602545, 2.4282112975892605, 3.3306353935909443, 2.185823360009586, 2.8722467137977987, 2.7720426273753516], \'MLPClassifier(hidden_layer_sizes=(50, 50), max_iter=2000, random_state=13)\': [3.8784808602464405, 3.652442882636654, 2.414295456519647, 2.5446784004946617, 3.1737280832904196, 2.8725869215031037, 4.911538830148408, 4.188815307932042, 2.724484146580634, 2.651367534729905, 4.602739110584875, 1.984505104387195, 2.972976985331631, 3.059982252612479, 3.6656916332262472, 2.1697154369474583, 0.5450292647469704, 2.623056687611636, 0.7492251798519469, 2.2981219682519107], \'MLPClassifier(hidden_layer_sizes=(100, 50, 25), max_iter=2000, random_state=13)\': [3.091507781863673, 0.5446362230976317, 0.5655935636886622, 0.5518877728745534, 2.8828433946603913, 3.9596293182430546, 0.5433121142851423, 2.218594801523848, 2.5495030899126148, 0.5643766472289381, 2.2220795976686016, 0.6463774756136758, 0.5711254687546714, 0.5984431446155191, 0.8399394293057193, 3.042407135563726, 0.6248247793367256, 0.5750337033697407, 0.6822132307181175, 3.6985681291008405], "SVC(C=1, kernel=\'linear\', random_state=13)": [0.8649854883575002, 0.7663138336871501, 0.79401496939446, 0.8168860774884295, 0.8762374654181798, 0.792672985350602, 0.8639588606141665, 0.7196014233766738, 0.9383777670765467, 0.8352709659235908, 0.8624973469191406, 0.8512150573616236, 0.8532716298281291, 0.7659522885994116, 0.8507049626768898, 0.803066180089058, 0.8406506515246747, 0.7674706757246004, 0.9254312214246103, 0.7909437926294417], \'SVC(C=1, random_state=13)\': [1.1145110669244493, 1.0240034800094193, 1.0800183236211574, 1.1059148354868271, 1.114292450460384, 1.0119123358621784, 1.091060673462963, 0.9875975739241802, 1.2097559249653522, 1.1424805091969017, 1.0914154346105602, 1.0476012872745535, 1.102391341676892, 1.0702827326108095, 1.067631486557756, 1.0587131651543054, 1.0807574862603984, 1.046911808438411, 1.1056683668042253, 1.068489425738346], "SVC(C=1, kernel=\'poly\', random_state=13)": [0.9017800973323225, 0.8035845648900131, 0.8424086164023881, 0.8424380526152511, 0.8894935268464805, 0.7944190167871693, 0.8771775558775986, 0.7808594852494181, 0.9988676086906559, 0.8719066967934455, 0.8994351638539928, 0.8650688714459694, 0.8895041492639847, 0.7917740488379879, 0.8760182587078148, 0.8522878500247565, 0.8771039310209795, 0.8036852339439132, 0.9375559464350928, 0.8405225431801925], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)": [10.896918466477281, 8.480859620968744, 12.57336746131994, 10.177031545162492, 10.896918466477281, 7.63277365887187, 8.382244974213291, 10.177031545162492, 11.316030715187946, 11.025117507259367, 9.220469471634624, 10.60107452621093, 7.963132725502628, 6.784687696774995, 8.382244974213293, 10.60107452621093, 9.639581720345287, 8.056816639920306, 8.801357222923958, 13.99341837459843], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=3)": [3.6596450357482584, 3.685004655030282, 4.972794738424214, 4.926513719523307, 4.951354325978084, 3.673465487347791, 5.239218249194433, 4.142438880275862, 6.164889106893452, 4.580792394551647, 2.8563990824380068, 5.347172205601723, 4.461521418876461, 2.8649266299629375, 2.787205564384661, 6.222493551380864, 4.051232591271347, 3.6673096268329144, 4.824214711029921, 9.12955466141535], "KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1)": [2.937330097593361, 3.359592606034505, 3.00761741226344, 3.3226156260684827, 4.991986086449721, 2.129197543969668, 4.532452555041519, 2.5868881035188633, 4.650678753859782, 2.6293128911858474, 2.148070705805738, 3.4286396479585894, 2.973953985451806, 2.1425893765556507, 2.128330089989587, 3.8019437447054742, 2.9507237813513485, 2.91275030758129, 3.287248828250679, 5.121001911928013]}'}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A1', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A2', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A10', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A5', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A3', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A6', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A7', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fada55085d0&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fadabfb3a50&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9985bdd0&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9422d890&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9985b7d0&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9985b810&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9985b710&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9985b690&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9985b5d0&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9985b510&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9985b3d0&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9985af10&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c1c0dd0&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0200b3c50&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa0200b3990&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa023095910&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa023134210&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0200b34d0&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0200b3850&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0200b31d0&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0200b3110&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01c1e9e50&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0200b2c90&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0200b2dd0&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024d017d0&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024a7afd0&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7036fe60d0&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70259c5f50&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70249fb6d0&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024d23050&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024d239d0&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024d231d0&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024d23950&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7030684250&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f700b630a50&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024d22810&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff92ff7d0&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff01062e490&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff992d810&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feffa3399d0&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feffa346050&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff938cb50&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff9993e10&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff9993d10&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff9993ad0&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff92e50d0&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff9993a50&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff9993850&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b101b7890&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b261b57d0&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b10e87010&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b10a4da10&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fd490d0&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b110d4050&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fb1c690&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fd49150&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fb1c8d0&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b1019a550&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b1019b590&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b1019b910&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b15ce3050&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b1021d650&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b101f6210&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b10243110&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fb9e750&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2aec75afd0&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b17fe7f50&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b17fe7d50&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fbf1910&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b0fb7a650&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b0fb79810&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b10273210&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223e10d0&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223adb10&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7022389a90&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70308e7610&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70246122d0&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024612d90&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024611990&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024a81f90&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024677e50&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024639e50&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70223e0a50&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024674950&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c755790&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c74a0d0&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fe40390&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fe0d850&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01f9de390&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fa00e10&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fa00dd0&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c7864d0&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c786690&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fa11e50&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01c78ee50&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa020103890&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9989c0d0&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fada5402910&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad991c85d0&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad99884750&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fada5417bd0&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fada56efe10&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad991cb910&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7fada56eced0&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7fada542af90&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad995cd110&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fada56ec1d0&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad998a1810&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff97455d0&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff971e950&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd4746390&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd470e010&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff91e6410&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff91e7910&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff005564a50&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff005566250&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd472b690&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff97450d0&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd472b210&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff005553cd0&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01f9f8950&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c780b90&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01f9ab610&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01f9ed850&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01f9cac50&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c7209d0&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c723bd0&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fdbe790&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fdbfbd0&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01c721e50&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fdbe8d0&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fdbc190&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff92ff850&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd47089d0&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff91d8190&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd470a750&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff938cb50&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff91ea290&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd4727e10&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff96e2110&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff96e2310&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd46f50d0&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff96e3310&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff96e16d0&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad94211810&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad99182010&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad99182210&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad991b6d90&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fadafabda50&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad989c44d0&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9899d650&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9899c850&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9899c6d0&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad991750d0&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9899e990&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad94170dd0&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223965d0&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223b0190&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70246685d0&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024ce0210&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024cf7610&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f700b65be90&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7f700b65bb10&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7f700b65b990&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7f700b65bd50&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024d01e50&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024678a50&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f700b65b790&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec73b090&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b0fbc4d50&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b10a6c450&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fbc6990&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fb1ead0&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2aec72afd0&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15e2c4d0&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15e2c410&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15e2c610&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15e2c550&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15e2c650&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15e2c910&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
     <t>{0: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A9', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A4', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: 'SVC(random_state=13)WITHOUT log_loss_field', 1: 'SVC(random_state=13)WITHOUT log_loss_field', 2: 'SVC(random_state=13)WITHOUT log_loss_field', 3: 'SVC(random_state=13)WITHOUT log_loss_field', 4: 'SVC(random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
     <t>{0: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 1: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 2: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 3: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field", 4: "aggregation_type='A8', random_state=13, order='xuyager'WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'RandomForestClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b15cd7910&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b10252fd0&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b15e79850&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2aec727cd0&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2aec755650&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b15e77e10&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15cf0590&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15cf2650&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15cf2250&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15cf0950&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15cf3150&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15cf3bd0&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c748d90&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa025c12210&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01f9f4350&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c76d850&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa025c3a0d0&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fe2d790&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c743e10&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c740490&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c742c90&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa025c39e50&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01c741ed0&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fa0ccd0&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70224146d0&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223c60d0&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024aa8210&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70223c4490&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024a5d4d0&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024a5fdd0&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024a5c150&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024a5f050&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024a5f710&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024a5fe90&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024d38a50&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024a5c510&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad989b6d90&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad995e9e90&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad98970910&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad995ea390&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9919b690&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9988d610&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad98973910&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9988c510&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9988dc10&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9988ec90&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9988df90&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad991584d0&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff00557ed90&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff00556e090&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff0055741d0&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff00556c790&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd47603d0&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd4761590&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd4762e90&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd4762990&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd47615d0&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd475d0d0&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd4762010&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd4761ad0&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fada5415650&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9896a190&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad991b6f10&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9896af90&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad998a3cd0&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad98959490&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9895bfd0&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9895b290&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad98959d90&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9895d110&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fada54141d0&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad98958810&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b0fbde210&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec704e50&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec764750&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2aec706950&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fbd2190&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b1026fe10&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b101e9910&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b10249950&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b10207dd0&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b10207b90&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b102079d0&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b10205290&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd46fd450&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7ff005570190&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd471ef10&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff005572210&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff91c3950&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff00557e410&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff00557db10&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7ff00557e390&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd46f3210&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff974d0d0&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff99e1710&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff99e39d0&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fa0c210&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c718190&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01f9c1a50&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fddd850&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fe3f610&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fdd6e50&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01f9b49d0&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fe1d650&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fe1f650&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01f9b1e50&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fe1fcd0&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa020101dd0&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024644950&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024d56950&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024650e90&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024d55b50&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f702462a190&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f702462afd0&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7f702462b6d0&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024628390&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024628f10&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024629e50&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024d605d0&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f702468b690&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa025c1a0d0&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fdf7450&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fe0b610&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c79d850&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c77d790&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa025c2b090&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa025c285d0&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa025c29ed0&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa025c2ac50&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01f9c9e50&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0200c2f90&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fe3d690&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec713050&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b15e69490&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec75c0d0&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fbde8d0&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2aec764c50&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b15cce210&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15ccf010&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15ccc4d0&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15e9e990&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b10226290&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15e97a50&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b15e96e90&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad991d7c10&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad98968050&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad998285d0&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad995a2ad0&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad989c6d90&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad995aad90&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad995e3910&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad9895cb10&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad998a9950&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fada54150d0&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad991c2810&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad991c1410&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7030bc01d0&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024d54350&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223b1f90&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f702462e950&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70308e6e90&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70308e5b90&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7f70308e6c10&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7f70308d7190&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7f70223d0210&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70223d1e50&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024640a50&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70223d2390&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff96ea310&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff96f5190&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff96dfbd0&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff96f5890&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd470fb50&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff99ab690&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff96eb910&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd473b850&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd473a390&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff96f5110&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7ff005555390&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff998d290&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff91f5650&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd472fe10&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff9199950&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff91d19d0&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff9734390&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff9737c90&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff919bb10&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff9734110&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff9737f90&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd47450d0&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff9737cd0&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd4756690&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9899da50&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9959b950&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9893cf10&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9918ccd0&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad989baad0&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad995aa7d0&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad995ab910&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad995aae90&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7fada5418250&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad995750d0&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fada54182d0&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fada5418790&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c719590&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fdc5310&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fa0b650&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0200d8dd0&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0200bded0&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa0200bc9d0&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fa04210&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01f9b4990&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01f9b64d0&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0200e9e50&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01f9b4750&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fdee950&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b0ffa27d0&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec73a810&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b10234350&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b1020ce50&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b10252210&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b15e93210&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b10241490&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b10240190&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b10241950&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2aec773c10&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2aec773910&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2aec773510&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024a71590&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7022404990&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024a3f650&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024656a10&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024647190&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70223f1f90&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024d3cb10&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024d3ed10&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024a6fdd0&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024a91e50&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70223f0a50&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70308dcc50&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01f9a8990&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c7289d0&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fdd0b90&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fdd5850&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01f9dd790&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fdcfb90&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fdcc9d0&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fdce950&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01fdcf390&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01c729e50&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fdcd650&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa025c473d0&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff96e6d90&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd475ef10&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd4752210&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd475c790&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff998c0d0&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7feff998d890&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7feffa290550&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7feff997b950&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd4718710&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff99d5110&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff998c3d0&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd471bd90&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024d44950&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024627190&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7024d3f5d0&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70223d9690&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024aafe10&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024aaea10&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024d585d0&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024d59f90&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7f702468ea50&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70223d9e50&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024d58a50&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f702468ea10&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad991a2ad0&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad99165650&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad995a5290&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad99164890&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad995d2210&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fada5432c50&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7fada5432b50&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7fada5432b90&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7fada5432750&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad9957d0d0&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fada5433650&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fada5433550&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b10226210&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b0ffd3c10&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b10233990&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b101fb290&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b10247ed0&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b10246950&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b10246d90&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b15e2d650&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2aec74cc50&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2aec74e9d0&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b0fb94c50&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b0fb959d0&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7030bbfb90&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223e6d10&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7022414490&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70223e6690&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70308e4510&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70308e73d0&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7f70308e7690&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7f70308e46d0&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7f70308e6390&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70223b9e50&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70223b8a50&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70308e68d0&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec737910&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b101dc750&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b1025a850&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b101ef010&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fbb6490&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fbb6d90&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fbc9610&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fbe9850&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fbebd10&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b1020a850&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b1020ad50&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b1020a910&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd4702390&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd47331d0&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd4778b10&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd4732210&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff005575750&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff005576fd0&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd470f210&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd470e050&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd470c1d0&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7feff99d50d0&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd470c4d0&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd470e990&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa027f41790&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c79fcd0&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01f9bb650&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c79d850&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01fdf0dd0&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c71ee50&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c71ded0&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0200f8490&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0200fb610&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01f9bd690&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa0200f9b10&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fdee5d0&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad989905d0&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9988cd10&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9988c710&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad989b6590&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad998b1a50&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad998b0810&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad98993910&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad998b0490&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad998b39d0&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad989ad0d0&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad998b3e50&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad998b00d0&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
-  </si>
-  <si>
-    <t>{0: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad98992ad0&gt;: [2.7464429198794944, 2.724577894933398, 1.7441089070842675, 2.706649239216259, 2.2766145967881664, 2.6476101527630154, 1.400389375452457, 3.0541182550283024, 2.7074576771336667, 2.705700685125449, 2.7138694808110206, 3.9454149727693113, 2.319447626065711, 2.6202435985318964, 1.7565971168411156, 4.070368087715867, 2.698130104271455, 3.585489476762915, 2.258808642131343, 1.8507452817668244], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad9917ed90&gt;: [0.9546443669906183, 1.3752288794043048, 0.975720275506026, 1.3896332323194531, 1.286303390388927, 1.3415328656128362, 0.9604170648725129, 1.3910419188857428, 0.9192877764593245, 1.3929931748610092, 0.9198332784085496, 1.3794182550815919, 0.949807514761639, 1.3888792992538688, 0.884827770032262, 1.377065582509961, 0.9096117069238108, 1.3950445640519793, 0.9372777599031413, 0.9273591865165012], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fad991a6bd0&gt;: [0.9433355169489218, 0.9541529745241163, 0.9162589950917133, 0.9570852334126274, 0.8837158934238222, 0.8915377669288637, 0.9262418444075247, 0.9591912577620529, 0.8779003648395294, 0.957879617424582, 0.9167583542583215, 0.9462355470564233, 0.9013919515975183, 0.9663347662794215, 0.8836158561303384, 0.9082139772170411, 0.9102370163783825, 0.9356530151949641, 0.8901009758598143, 0.9450801241706582], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad9917e990&gt;: [4.471338310579529, 4.717753456622716, 6.181935181697869, 4.713375177896516, 6.870270974970844, 1.7678589140170335, 2.2701522899110738, 3.0562917206238733, 4.529726432479017, 3.243830960279054, 0.6039748251082637, 2.306325371588359, 2.0213648537465025, 2.6136856205793144, 5.510819319709534, 3.9539877089081243, 4.617775323621794, 2.095633399441972, 4.332202596440598, 0.5952339508232573], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad995a9f10&gt;: [2.974152291825751, 3.147591701848447, 2.3287348871162896, 0.6394026178502985, 2.0953794226463494, 2.5753083153041194, 0.7261901713938768, 3.541383394727076, 3.9832685057026613, 2.79427996329385, 0.6538988041693709, 2.7066025702160035, 2.872685389676998, 2.3766216743794657, 2.5032924843925564, 0.8415147982405509, 2.6829861480777866, 0.7017473786646647, 2.33731542194944, 0.7273517726003067], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fad995a8290&gt;: [0.6318336605306103, 0.7947740564791416, 2.480727989376591, 0.8073399508611804, 0.6454976213691032, 0.5741121794000205, 2.3529095265950293, 2.9196513263482227, 2.40069284958483, 0.682549121462116, 0.5711612303870259, 3.616421612982365, 2.911875376596917, 0.6460915649472436, 0.4952917148184953, 0.7561035648753647, 0.5833485139347098, 0.9956443983955378, 0.6628591528182042, 0.5707912791584434], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad995aa3d0&gt;: [0.8236336008758759, 1.003729183307348, 0.9287460828742373, 0.9747492143986854, 0.8468456877020675, 0.9509444784525805, 0.7943881770815563, 0.9672035067019059, 0.8363729799903108, 0.9615569050096213, 0.8222261086487308, 0.9244703126114301, 0.905882099650164, 0.9348568308144124, 0.8189358473245977, 0.9917987034300474, 0.8438139639932579, 0.9922875530967298, 0.8781584124192605, 0.8954381773333843], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad995a8810&gt;: [1.065479096207076, 1.1393718798768793, 1.1053115234752453, 1.2706436644615302, 1.0407069513259428, 1.1260869353719807, 1.039645374887679, 1.1393336742108577, 1.0264042842268803, 1.1648488586602743, 1.0542016433350851, 1.1261050567408482, 1.0411870844912892, 1.1519245977856154, 1.0268942102310439, 1.1264236887832018, 1.0800694625825629, 1.1656540793453434, 1.1592935249094694, 1.112097176763969], &lt;method-wrapper \'__str__\' of SVC object at 0x7fad995ab7d0&gt;: [0.8652246834132751, 1.0058966539212952, 0.9572329560177993, 0.976565973378657, 0.8885543188934655, 0.9790607372071287, 0.8490721489858744, 0.9953415528342786, 0.8778133250924633, 1.042658729410742, 0.8376210148499513, 0.9531497402067114, 0.9209095886580906, 0.9498171770945119, 0.8594313276600386, 1.0072695046849378, 0.8755172987527601, 1.0072458796780674, 0.9195222155950444, 0.950039260074859], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad995d50d0&gt;: [10.43368913895497, 11.856464930630645, 9.485171944504518, 11.856464930630645, 10.43368913895497, 9.01091334727929, 8.062396152828839, 13.279240722306321, 9.01091334727929, 12.330723527855872, 9.01091334727929, 9.010913347279292, 9.959430541729743, 9.010913347279292, 7.113878958378389, 10.43368913895497, 8.062396152828839, 10.907947736180192, 10.43368913895497, 9.959430541729741], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad995a97d0&gt;: [6.833739991354622, 5.477906256721475, 5.0174173474900545, 9.148761054862119, 4.1191512715891925, 5.89055786411612, 3.630437249513071, 8.270971207881196, 5.502346079139178, 6.857315773844465, 4.53850941990997, 6.3861567301891435, 6.4050831823241285, 4.120701048374145, 3.1181474449471063, 5.499246525569274, 4.141177277294083, 6.896896757970157, 6.83752528178162, 4.113816204377243], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fad995a8710&gt;: [5.574727619121732, 4.666625751004311, 2.4189820395712682, 6.471857814273318, 1.9322063204366977, 3.7440833068962545, 2.3931707434393807, 3.8233938804978838, 2.8815727059547482, 5.132239504361851, 2.8499761987187293, 4.209758677989379, 5.547602139169801, 3.3403632330509705, 2.8096076412610214, 3.333043094022147, 2.8765496983035526, 3.773531288104892, 5.134475018003896, 2.3651707025407718]}', 1: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f7030bc6690&gt;: [2.3520757887755024, 2.245835895015536, 2.735025430862919, 2.272184322654269, 2.7274523765572116, 3.6791918256378833, 2.7848040435038137, 1.3487370854681608, 2.7842206775324976, 1.7617657219799925, 3.638703040571574, 2.1687498724273926, 1.3648416501272194, 2.207699843337308, 2.2386335101436003, 3.232328694796274, 2.7487956532675755, 2.3587941706993307, 1.3197769934393317, 1.8907376884764802], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70223adb50&gt;: [0.954871398462486, 1.3833987109473809, 0.9461148688278604, 0.9475249142952763, 1.3935227637473875, 1.3674876928850264, 0.9182649033190262, 0.8855503770591102, 0.9283156921187207, 0.9372754599974109, 0.978268751022146, 0.9194266627539411, 1.3492316461765335, 0.9657480126713929, 0.9376966369700895, 1.4042221230916976, 0.94290049360025, 0.9715108345151996, 0.9476286921915896, 0.9770060118347528], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f70308d0550&gt;: [0.9336491564855067, 0.9327078146259326, 0.9318602543658454, 0.9343805405782789, 0.8966241246137175, 0.9380058086771107, 0.9049947891966695, 0.885336781925937, 0.9373647758948023, 0.9527040166498305, 0.9369248732106983, 0.9249039795229205, 0.9280445067235314, 0.9107787976474583, 0.891909495665401, 1.3649157050088323, 0.9422045795782162, 0.9532642241637396, 0.9071017680991654, 0.9586868161368706], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70223ade90&gt;: [4.932366371844175, 5.106768639289368, 2.4013300193229283, 4.222659406469825, 0.7344474867429205, 2.7669493802291134, 2.7185764529061363, 4.4558498069144985, 4.4413482144113186, 4.2070978408217625, 3.729371436898344, 2.842049786594675, 1.9220949711861708, 1.9491304902153097, 5.614293547650547, 3.4278604459878728, 3.575988791061824, 2.4268794041320185, 5.05638297770841, 3.6684157263966792], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f70308f7190&gt;: [2.313530674621134, 2.8356782676954384, 2.4735740167659155, 0.6746762113675625, 0.77533960090571, 2.9865437481719903, 4.459328257185085, 2.799324909175586, 3.161563485539338, 0.6414907791164691, 0.6692361911643037, 2.847989424165028, 2.621145307724852, 3.293509735129921, 2.2456084633689897, 2.9193386931794363, 0.5040276624322229, 3.030250593428063, 2.476953953379598, 0.6678316901682511], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f7024674310&gt;: [0.7113515213646792, 1.862560166958891, 0.6970017229745822, 0.8465689300930307, 3.0234428861980907, 0.6448671090421225, 1.8564502046381823, 0.6174828932368028, 0.63802527751843, 0.6054763658248247, 0.7967755792847552, 0.7016353932290376, 2.477000384723876, 0.6827898465130603, 2.6771977681372987, 2.11039962923876, 2.7834235388894597, 0.7469684619330377, 0.5487348608190024, 2.9036858079312045], &lt;method-wrapper \'__str__\' of SVC object at 0x7f70246748d0&gt;: [0.9594064609094503, 0.8897960443750731, 0.866428453966548, 0.8903106853774334, 0.9425388929965532, 0.9893188134024211, 0.8918996803586126, 0.9306657682751966, 0.8786594194990519, 0.9170725333691543, 0.958084899473929, 0.8350438525468492, 0.9634115304091057, 0.8619933298647062, 0.9038615285658286, 0.8843575906239124, 0.9310303586045044, 0.985623413763481, 0.8520082859375796, 0.9293027646740435], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024675810&gt;: [1.1655478053625163, 1.0996284030904908, 1.2059190036036675, 1.1643656414248142, 1.1270196572012297, 1.1395336105816227, 1.1255363128218232, 1.2050651166043078, 1.1386537483796149, 1.165468748364403, 1.2405229246360894, 1.085977317404663, 1.1661233132870916, 1.0864472347053968, 1.1520023739265335, 1.1115214121603103, 1.1399828692829463, 1.191520306938844, 1.2046856745706602, 1.1397295362938984], &lt;method-wrapper \'__str__\' of SVC object at 0x7f7024674550&gt;: [1.0012997749047223, 0.9456143662713675, 0.9476129214336474, 0.93264295581548, 0.9715044820421936, 1.0444245375244008, 0.947310408213359, 0.9592871970770004, 0.9209526750659446, 0.9458369036372267, 1.0001851328640001, 0.8770850685364353, 1.0576606735175595, 0.9041216469546169, 0.9060536128650646, 0.9436627306078568, 0.9729867871564175, 1.0017130893564032, 0.9203122813928498, 0.9719436074544575], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7030a41e50&gt;: [9.485171944504517, 11.38220633340542, 9.485171944504517, 9.485171944504517, 9.959430541729741, 11.38220633340542, 9.485171944504517, 6.165361763927936, 12.330723527855872, 9.01091334727929, 9.485171944504517, 10.907947736180194, 10.907947736180194, 9.959430541729741, 10.43368913895497, 10.907947736180194, 9.959430541729743, 13.753499319531551, 12.804982125081096, 10.907947736180192], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f70308e8a50&gt;: [4.981621653791359, 6.437093585595825, 5.547947867333911, 5.445210116592686, 5.522136571202023, 5.964384765155552, 5.05389877804584, 5.030322995555998, 7.383375266404235, 5.471885452652434, 6.864200617841367, 4.588074801602468, 5.948379563519705, 4.135156473225041, 6.433308295168828, 6.029091308556039, 4.607865293665315, 8.29076169994404, 7.861419154056458, 5.426283664457701], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f7024677cd0&gt;: [3.320511123252541, 4.255048406623358, 3.828478505884664, 4.667162882511156, 4.248777160729146, 3.7497920514045426, 2.46304889984131, 4.191891640007824, 4.30466055719118, 4.185855987078522, 5.1341629584431425, 2.4305778316586113, 4.671812212866014, 2.901736875313933, 5.6423405641610955, 4.259207374346693, 3.3344910343321765, 4.298951812682892, 5.221330802580441, 3.259901929839806]}', 2: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff96dee90&gt;: [3.0707068226354677, 2.7353121205445947, 2.6933143118435248, 2.21192290224794, 2.572718356255873, 2.1742623643409735, 2.2436471502488144, 1.7379326035707108, 1.754830757286917, 2.2628567497920575, 2.7486932823817996, 1.340521520907266, 2.7515206511720054, 2.17953033250306, 2.2660000643747202, 2.7193625209191983, 1.7731449312980887, 3.216540075929671, 3.165652462850025, 0.8788102777227589], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fefd473a210&gt;: [1.3524386907611028, 1.3745823757582678, 0.93977184115169, 1.738602852011488, 0.8975866336863412, 0.8784655631172448, 0.9496228974822386, 1.3161425544398317, 0.9310072239942436, 0.943197662347713, 0.9803077563534854, 0.9043701155964523, 2.2506762246196828, 0.9001121486512133, 1.363943909342869, 0.8979164474172354, 0.93878986695921, 1.4174226772167933, 1.7792177405162493, 0.9444729024387233], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7feff9718190&gt;: [0.920710428288794, 1.3241632638326708, 0.9139123646670055, 0.9075763395165288, 0.8797422129900976, 0.8767710711218406, 0.9372791245738309, 0.9067727289960374, 0.9316908555712576, 0.9330942662561201, 0.8960185095596946, 0.8952175724446781, 1.3783941209358497, 0.914844892149102, 0.9342213212644696, 0.8952411390293217, 0.9374458199903565, 0.9541002175010499, 0.9292833723210147, 0.9301817154831339], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7ff00554a850&gt;: [0.6460036053679334, 4.5813012255056975, 0.7439578223443781, 3.1005048372021093, 4.136945080703254, 3.2751834792226036, 4.186928864901398, 4.641881289877767, 4.684634575377135, 4.576248212249142, 1.8726753799803508, 4.181843783611579, 5.030280152463415, 1.7231801927498787, 0.6473649299043736, 1.7734484307880556, 3.000140450215201, 0.6172477339209256, 3.755311452034053, 3.299248211144224], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd47595d0&gt;: [0.6950959121293225, 0.6313633865518152, 0.6995462618377281, 0.5518009308329936, 2.642608620756119, 0.6042303172100971, 4.503744538573172, 0.6607827584016047, 2.4134014087424855, 0.6925176784731057, 0.8929841000065096, 2.7426195905588115, 0.7247864929695426, 2.2125170981155002, 2.664338462550301, 2.899291466883294, 2.896980423341163, 2.240258252675349, 0.6475405598955035, 2.5382461612026987], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fefd4759090&gt;: [0.6128405860343649, 0.7123248453584686, 0.6355247896715353, 2.3540531259679796, 1.9395411174878998, 0.6782449602221561, 0.6588419822068835, 2.299257340233248, 0.6860916346871498, 3.578819813620069, 2.4810073233117413, 0.5897613379929734, 2.827757499718554, 2.7792586042661482, 0.6284037270437484, 0.5437783721768653, 0.5461345392111678, 3.3058952532792305, 0.6214305420347584, 2.9836618936842836], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd4758990&gt;: [0.8941788172241502, 0.8767721702719194, 0.8673691920633682, 0.8474132338841563, 0.8928293519430589, 0.9429984786582387, 0.9096319285996696, 0.983535045093103, 0.9324456351196502, 0.9307642898520668, 0.9222051732538695, 0.915139032487861, 0.8687165001179649, 0.9814796852889781, 0.8687790896494668, 0.8381819004924952, 0.8654631970933925, 0.9036205839876202, 0.9239648965151274, 0.8860854023419549], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd4759b50&gt;: [1.1187110392288149, 1.1246616057067242, 1.1701496979650834, 1.0979073979933465, 1.1320338661545266, 1.1241126686680867, 1.134333000399869, 1.1381330818570083, 1.158232521377124, 1.1117776951135352, 1.0945427975434279, 1.1114105942216395, 1.1575695963245138, 1.1762647080558328, 1.1578303527443985, 1.1110503830775134, 1.1174312480751718, 1.1242352519765257, 1.1978251907466382, 1.0944230709779266], &lt;method-wrapper \'__str__\' of SVC object at 0x7fefd475be10&gt;: [0.895928771344861, 0.9189339492574483, 0.8958480424851418, 0.9024476527541926, 0.9079501767549626, 0.95870201024188, 0.9239987253447852, 1.0245022347349007, 0.9343115758437025, 0.9595364810898299, 0.9369410414901335, 0.9581477381924324, 0.8835818231170574, 0.9972842463417703, 0.8965718988150052, 0.8796829788399873, 0.8803876577119584, 0.9819860667817161, 0.9383293856757455, 0.9424847568118245], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd472d110&gt;: [8.062396152828839, 11.38220633340542, 9.485171944504517, 10.907947736180194, 11.38220633340542, 10.907947736180194, 13.279240722306323, 11.38220633340542, 12.804982125081096, 9.485171944504518, 12.804982125081098, 10.907947736180192, 9.959430541729741, 10.907947736180194, 10.43368913895497, 12.330723527855872, 9.959430541729743, 11.38220633340542, 9.485171944504518, 11.382206333405419], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd475bd50&gt;: [3.6395576071520175, 5.947693826662611, 5.47567074307943, 5.549497644118864, 5.499246525569273, 8.248945202176305, 6.45086327358963, 6.918922763675045, 5.9568141843015585, 6.902231825182108, 6.067122515896777, 4.105381583595389, 5.044092683549801, 5.522136571202024, 4.561399465542721, 6.031326822198085, 4.589624578387421, 5.032558509198042, 5.075239046893639, 4.620770941731259], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fefd475a090&gt;: [2.337824478484192, 4.65719333380461, 3.295236958627499, 3.3007206311896957, 3.3021218026244012, 3.281717712458866, 3.74908094466837, 4.665551487990619, 4.649607904090356, 4.68796601985211, 3.872280075469274, 2.417058585489978, 4.148852273876149, 3.3239227363832007, 4.200536483875509, 3.387601785645319, 2.8616187596813956, 4.638876151930872, 4.219938449781756, 2.430889891219365]}', 3: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2b15cd3050&gt;: [1.7803855958685026, 1.8007446050424043, 1.3577063643051475, 1.819417607489654, 2.195973302622544, 2.222891125741469, 2.2711810449221432, 1.8058113737063568, 2.1819407973950224, 2.694329964984197, 2.5995398242141534, 2.187272856744406, 2.6349579543848076, 2.22248819233435, 3.091939773694063, 2.295299440233111, 2.694656873405212, 3.19716100645079, 3.1253419808544844, 2.2487287677730277], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec71fcd0&gt;: [1.3205044153153405, 1.3223047478135939, 0.8967859141070355, 1.3446441649931216, 0.9290513771797679, 0.9382082430430925, 1.4211945756905817, 0.8726272717868193, 0.9347933107457859, 1.4412355552573834, 0.9204668172434739, 0.9191766183804361, 1.3589935437987655, 1.7807176712690131, 1.3494843409653001, 1.8681204906730084, 0.8969779286470136, 0.9246835682637599, 1.7831878950721531, 0.9364148220371786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7f2aec71e990&gt;: [0.9068330701922901, 0.9171914168171964, 0.8871239856534309, 0.9382466974347724, 0.8954639974933721, 0.928708985307086, 1.335611617371986, 0.8651744130780353, 0.9032580954611312, 0.9682040500625894, 0.9035435488514072, 0.9268149022421978, 1.3694948963615174, 0.9474736903685055, 0.9111772513559174, 0.9526142418831597, 0.8726055557721842, 0.9051125300632412, 0.8792400403582329, 0.9183067269558068], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2aec71e210&gt;: [2.316841682492044, 0.6509654024710972, 4.4245373338444205, 5.347389586298977, 2.2852436154057956, 1.7211186134110643, 2.4303858571471384, 2.0345079422283088, 3.711570684843178, 2.653276024432618, 4.4631351678616555, 1.6288024730439052, 0.7050337554436649, 3.9396341796395307, 2.047349757370122, 3.5707837011410772, 0.5990711915869745, 5.285488808808075, 3.33767825691872, 2.234419852101182], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fb787d0&gt;: [4.318000106893838, 2.378996757238289, 3.7499127578310234, 4.475315306649129, 2.9415839602091283, 4.827120584045979, 2.5187079363933575, 2.7435880196262996, 2.835659634004876, 2.60294111678897, 0.6643429588900309, 3.087300188827684, 3.6686335681469564, 2.2437217223826997, 3.1141046091186095, 0.5907577728668655, 0.5918123050640264, 1.895395828581271, 3.943124461652465, 2.3930716310262308], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7f2b0fbad650&gt;: [2.6335226180814404, 3.0978287107286877, 2.0337475720466296, 0.507821407245127, 0.5725690120381688, 2.957088279564732, 2.8508675108157524, 0.6595818746592614, 0.6304940451761866, 0.6622626173046712, 2.2444225049736883, 0.5806239844819441, 2.845654239616614, 2.528379957728378, 0.6518487151908321, 2.705564236186939, 0.5625370389606631, 0.5770187992170609, 2.239207441132175, 2.0276604662517226], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b17feabd0&gt;: [0.868031932378155, 0.9023926532023333, 0.9598074492564784, 0.818358070024872, 0.8930821270588254, 0.9124885301484549, 0.9224553756783836, 0.9175332306453846, 0.8651697161954033, 0.8612575006290455, 0.8530019452493022, 0.8632853618481718, 0.8445107639657655, 0.8720223988347272, 0.8540541706756608, 0.8612856935065017, 0.8506848331693511, 0.8622184195210079, 0.9074185898145607, 0.8744763453271477], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b0fbb2210&gt;: [1.0931123133754053, 1.13774082075641, 1.1977553062267257, 1.1236053825816068, 1.1328923292767688, 1.1107520816720444, 1.1866367827488693, 1.0985943018766313, 1.1056683763419077, 1.110384279534084, 1.1593288853921841, 1.0850745290482686, 1.1444213845585143, 1.110962880518161, 1.1559868019333148, 1.1502762567677631, 1.1832752322162647, 1.1230381487847294, 1.1583057281664386, 1.1510513253133103], &lt;method-wrapper \'__str__\' of SVC object at 0x7f2b17ffa590&gt;: [0.8833646455793619, 0.970118307433443, 0.9879860557418975, 0.8475992723460237, 0.9080951448662261, 0.9549614688941707, 0.9502427472211834, 0.9604689655241309, 0.90712447456957, 0.8632297997177577, 0.8813678897557727, 0.8922014929894316, 0.8721393344227105, 0.9009647289530642, 0.855899162855532, 0.890138366207664, 0.852626750972159, 0.8778374051103757, 0.9093005259113475, 0.9436451854580546], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b17ffb990&gt;: [7.113878958378389, 10.43368913895497, 7.588137555603614, 8.062396152828839, 8.536654750054065, 10.43368913895497, 8.536654750054064, 9.959430541729743, 8.536654750054064, 8.062396152828839, 9.959430541729741, 7.588137555603613, 6.6396203611531615, 10.907947736180192, 6.6396203611531615, 12.804982125081096, 9.485171944504517, 10.907947736180194, 11.38220633340542, 5.69110316670271], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b17ff8850&gt;: [4.0232983648448695, 4.119837008446285, 3.1637492331418398, 3.2017804404825787, 4.5416089734798755, 5.961285211585648, 2.660579786214821, 5.940808982665709, 3.6738035240657596, 3.196445373270629, 5.5007963023542255, 4.492221894858145, 3.15841416592989, 5.076788823678591, 4.104695846738297, 5.0797100741777275, 3.6197671150891715, 7.773136828166127, 3.7118347314064986, 3.5641809293276316], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7f2b0fbf1850&gt;: [3.2415126092116657, 3.319600314449358, 2.356525858673087, 1.882205643712277, 2.360162543749838, 3.80382846038113, 2.3127859068240597, 3.276070585686162, 3.317800095839235, 3.251957671689474, 4.2364956317847104, 2.3267042001681104, 2.8038988967527336, 3.3444605830387233, 3.7711939379879236, 3.29015233324072, 2.3739790006189647, 3.7337400808933703, 2.8845088053141454, 3.194074354550305]}', 4: '{&lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01fe1ded0&gt;: [2.2704889483816353, 1.743962775185734, 4.494449025124781, 1.7953140610389469, 2.2185826742987502, 2.7530157043156422, 2.1700393054303415, 2.201564827384795, 3.101535645104271, 2.1363682653110705, 2.2278054028234733, 2.7263225115330685, 2.592286784235193, 2.7183991179681284, 1.812179416370953, 2.3138318848972177, 2.1716914531010696, 2.252767507887761, 2.5382533831211713, 1.18103880722786], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c750990&gt;: [1.320942369117954, 1.3310631889276148, 0.958912087257777, 0.8844382695345407, 1.3076855219298933, 0.9457655646815164, 1.37274331868587, 0.9113818497273012, 1.7544870536240194, 0.920143712182513, 1.346794575372334, 0.8769835913964159, 1.345683426608953, 0.899477303097048, 0.9331731523737264, 0.9334006459374659, 1.4091549659969633, 0.9167692120338851, 0.9257237074416192, 0.9053373275289455], &lt;method-wrapper \'__str__\' of RandomForestClassifier object at 0x7fa01c765790&gt;: [0.9068297633210656, 0.9214321923714214, 0.9130922066993898, 0.8864564104671914, 1.2973826048217325, 0.9387839885597296, 0.9559434405385829, 0.8971731088471456, 0.8923643484376281, 0.9118745632886605, 0.9191074893354113, 0.87851604570398, 0.8970014915376304, 0.8684012166958232, 0.9419436908973955, 0.8884698817989835, 1.3800490683012747, 0.9362293883283985, 0.8877484033910154, 0.8947778551376232], \'removed_models\': "[KNeighborsClassifier(metric=\'manhattan\', n_jobs=-1, n_neighbors=1)]", &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c765850&gt;: [0.6512735121047608, 2.854611906444691, 4.963988288565822, 2.1047761735754, 6.145763845481219, 2.293813995202905, 3.8476020037575993, 3.627222932779676, 2.509988486478509, 4.3814893936927195, 3.984017538322286, 4.710573786731384, 0.7594120114307066, 1.7413211868041718, 3.985842266964068, 4.787539587082077, 4.147520669503565, 2.943525319384332, 3.755565059774659, 3.7758410814274925], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01c7505d0&gt;: [3.226271665248356, 2.8069309745967623, 0.745151162982013, 0.5849157747580042, 3.54223271879843, 1.766738999178516, 2.9163922576553483, 2.9806428231844846, 0.6637395210685216, 2.1408195942414534, 4.321737887580603, 0.6011901279750813, 2.262548000655554, 2.42610100089138, 0.5899124939609698, 4.079881229061007, 0.6684848527174201, 2.502791809970978, 0.7445669244917436, 0.5232496475606618], &lt;method-wrapper \'__str__\' of MLPClassifier object at 0x7fa01f9ff210&gt;: [0.5767927333510009, 0.8614581745331601, 2.001185204009174, 1.6200139150554984, 0.5911818980675371, 0.6463683111860895, 2.86677662585734, 0.5985225600765643, 0.5888314902643312, 0.5317951176960672, 0.6485151560671552, 0.5138197304024997, 0.7872766296294632, 0.5032958272092933, 0.6586331549015559, 0.6055370190719774, 0.5881709802612968, 1.9332007887379554, 2.3440962426149317, 0.594338813658876], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01f9ff390&gt;: [0.9762113660158135, 0.8869982283225156, 0.9890026605658873, 0.8999870483039153, 0.8923693094474694, 0.9736084268674101, 1.0063934180562208, 0.8160596858491431, 0.9361796258581062, 0.8730344947219725, 0.9903540442754352, 0.8723003933594797, 1.0312889892353159, 0.8049668307265554, 0.9119472758390579, 0.9390714084131705, 0.8925425030984794, 0.915417946056534, 0.9787239712838357, 0.8183541637802179], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa01c775690&gt;: [1.1521045260425944, 1.0262670968716643, 1.1652647342014741, 1.0795480317997024, 1.1125919716721866, 1.106257717432659, 1.1779402968434707, 1.106010097187817, 1.1650948067137095, 1.052558143631215, 1.1777629169083585, 1.0342116635860557, 1.1391820802324821, 1.0271553215458191, 1.1646243674073247, 1.1590718303909398, 1.1251614149807132, 1.105828973050512, 1.1123525961373528, 1.0398294121764284], &lt;method-wrapper \'__str__\' of SVC object at 0x7fa0200cb950&gt;: [1.0171939551629323, 0.9027140162321283, 1.0046110625958387, 0.914785913164544, 0.9342599285481326, 1.0284050282311066, 1.0614256764562504, 0.8315960528848866, 0.9382403976375995, 0.8873725067235665, 0.9920023120354889, 0.901269501461955, 1.059056583071097, 0.8967404843326648, 0.9531312381976802, 0.9419681464982748, 0.9079659077385289, 0.9447939152822785, 0.980375824395091, 0.8212048384520951], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01c751e50&gt;: [11.38220633340542, 11.38220633340542, 8.536654750054065, 11.856464930630647, 8.06239615282884, 9.959430541729743, 12.330723527855872, 12.330723527855872, 9.959430541729741, 8.536654750054065, 9.959430541729741, 9.959430541729743, 9.485171944504517, 10.43368913895497, 8.062396152828839, 13.279240722306321, 9.01091334727929, 9.485171944504518, 9.485171944504518, 10.433689138954968], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fdf4590&gt;: [6.918922763675049, 6.433308295168827, 3.596877069456421, 8.371473444980378, 2.754882916174193, 7.317118946218795, 7.813403549148911, 5.964384765155552, 6.887776400331208, 4.105381583595389, 7.32090423664579, 4.545394263906872, 6.422638160744929, 4.604765740095409, 3.6144320478772225, 5.555518448187906, 6.866436131483414, 5.9826254804334456, 6.4295230047418315, 4.574305113608665], &lt;method-wrapper \'__str__\' of KNeighborsClassifier object at 0x7fa01fdf6cd0&gt;: [4.710304085117754, 3.80938859953917, 3.7077653305509752, 4.375449522396292, 2.4064500688016626, 5.125830174136212, 4.732493545033152, 4.6692497908029535, 4.288593737819747, 3.3042956985308614, 6.052858494388618, 2.8700533804632506, 4.6776079449889645, 3.3289308951741354, 3.254581711488117, 4.315269073879494, 4.675597503293011, 3.807450296597619, 5.138797439937739, 3.808539408471571]}'}</t>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 1: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 2: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 3: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field', 4: 'BaggingClassifier(n_jobs=-1, random_state=13)WITHOUT log_loss_field'}</t>
   </si>
   <si>
-    <t>{0: 'SVC(random_state=13)WITHOUT log_loss_field', 1: 'SVC(random_state=13)WITHOUT log_loss_field', 2: 'SVC(random_state=13)WITHOUT log_loss_field', 3: 'SVC(random_state=13)WITHOUT log_loss_field', 4: 'SVC(random_state=13)WITHOUT log_loss_field'}</t>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=7),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
     <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=7)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=3),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=3)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=3),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+    <t>{0: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 1: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 2: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 3: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 4: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
+  </si>
+  <si>
+    <t>{0: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 1: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 2: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 3: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 4: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field'}</t>
+  </si>
+  <si>
+    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
   </si>
   <si>
     <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                  n_jobs=-1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=7),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsOneClassifier(estimator=KNeighborsClassifier(metric='manhattan', n_jobs=-1,\n                                                  n_neighbors=1),\n                   n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 1: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 2: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 3: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field", 4: "KNeighborsClassifier(metric='manhattan', n_jobs=-1, n_neighbors=1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 1: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 2: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 3: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field", 4: "OneVsRestClassifier(estimator=KNeighborsClassifier(metric='manhattan',\n                                                   n_jobs=-1, n_neighbors=1),\n                    n_jobs=-1)WITHOUT log_loss_field"}</t>
-  </si>
-  <si>
-    <t>{0: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 1: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 2: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 3: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field', 4: 'DecisionTreeClassifier(random_state=13)WITHOUT log_loss_field'}</t>
-  </si>
-  <si>
-    <t>{0: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 1: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 2: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 3: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field', 4: 'MLPClassifier(max_iter=2000, random_state=13)WITHOUT log_loss_field'}</t>
   </si>
 </sst>
 </file>
@@ -692,47 +668,41 @@
       <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" t="s">
-        <v>48</v>
-      </c>
       <c r="F2">
-        <v>0.9282506088855295</v>
+        <v>0.9386904761904763</v>
       </c>
       <c r="G2">
-        <v>0.01963433199176793</v>
+        <v>0.04968009908301269</v>
       </c>
       <c r="H2">
-        <v>0.8789473684210527</v>
+        <v>0.7789473684210527</v>
       </c>
       <c r="I2">
-        <v>0.03569647359539615</v>
+        <v>0.02105263157894739</v>
       </c>
       <c r="J2">
-        <v>0.6534391534391535</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="K2">
-        <v>0.03966489907723028</v>
+        <v>0.01428571428571428</v>
       </c>
       <c r="L2">
-        <v>0.672298495155638</v>
+        <v>0.465374149659864</v>
       </c>
       <c r="M2">
-        <v>0.05339221287350029</v>
+        <v>0.01369088815030672</v>
       </c>
       <c r="N2">
-        <v>0.6534391534391535</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="O2">
-        <v>0.03966489907723028</v>
+        <v>0.01428571428571428</v>
       </c>
       <c r="P2">
-        <v>0.6502858336316983</v>
+        <v>0.4910966810966811</v>
       </c>
       <c r="Q2">
-        <v>0.03971623462340463</v>
+        <v>0.01381726439081917</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
@@ -740,49 +710,49 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
         <v>48</v>
       </c>
       <c r="F3">
-        <v>0.9282506088855295</v>
+        <v>0.9354166666666668</v>
       </c>
       <c r="G3">
-        <v>0.01963433199176793</v>
+        <v>0.05082754790318277</v>
       </c>
       <c r="H3">
-        <v>0.8789473684210527</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I3">
-        <v>0.03569647359539615</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J3">
-        <v>0.6534391534391535</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="K3">
-        <v>0.03966489907723028</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="L3">
-        <v>0.672298495155638</v>
+        <v>0.5746031746031746</v>
       </c>
       <c r="M3">
-        <v>0.05339221287350029</v>
+        <v>0.07800097550281197</v>
       </c>
       <c r="N3">
-        <v>0.6534391534391535</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="O3">
-        <v>0.03966489907723028</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="P3">
-        <v>0.6502858336316983</v>
+        <v>0.5849293563579276</v>
       </c>
       <c r="Q3">
-        <v>0.03971623462340463</v>
+        <v>0.08572400972502163</v>
       </c>
       <c r="R3" t="s">
         <v>50</v>
@@ -790,252 +760,252 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
       </c>
       <c r="F4">
-        <v>0.9200921726715376</v>
+        <v>0.9348214285714285</v>
       </c>
       <c r="G4">
-        <v>0.01292524646669384</v>
+        <v>0.05119912717598579</v>
       </c>
       <c r="H4">
-        <v>0.8947368421052632</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I4">
-        <v>0.01664356663246513</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J4">
-        <v>0.662962962962963</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="K4">
-        <v>0.03128411745840102</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="L4">
-        <v>0.6827994227994227</v>
+        <v>0.5746031746031746</v>
       </c>
       <c r="M4">
-        <v>0.0441886908736302</v>
+        <v>0.07800097550281197</v>
       </c>
       <c r="N4">
-        <v>0.662962962962963</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="O4">
-        <v>0.03128411745840102</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="P4">
-        <v>0.6611504952858337</v>
+        <v>0.5849293563579276</v>
       </c>
       <c r="Q4">
-        <v>0.02923617905225985</v>
+        <v>0.08572400972502163</v>
       </c>
       <c r="R4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>48</v>
       </c>
       <c r="F5">
-        <v>0.9197982279331486</v>
+        <v>0.9324404761904763</v>
       </c>
       <c r="G5">
-        <v>0.01336297467445048</v>
+        <v>0.05252449218137729</v>
       </c>
       <c r="H5">
-        <v>0.8947368421052632</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I5">
-        <v>0.01664356663246513</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J5">
-        <v>0.662962962962963</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="K5">
-        <v>0.03128411745840102</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="L5">
-        <v>0.6827994227994227</v>
+        <v>0.5746031746031746</v>
       </c>
       <c r="M5">
-        <v>0.0441886908736302</v>
+        <v>0.07800097550281197</v>
       </c>
       <c r="N5">
-        <v>0.662962962962963</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="O5">
-        <v>0.03128411745840102</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="P5">
-        <v>0.6611504952858337</v>
+        <v>0.5849293563579276</v>
       </c>
       <c r="Q5">
-        <v>0.02923617905225985</v>
+        <v>0.08572400972502163</v>
       </c>
       <c r="R5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
         <v>48</v>
       </c>
       <c r="F6">
-        <v>0.9184857646762408</v>
+        <v>0.9315476190476192</v>
       </c>
       <c r="G6">
-        <v>0.01423691816830781</v>
+        <v>0.04916572984233737</v>
       </c>
       <c r="H6">
-        <v>0.8894736842105264</v>
+        <v>0.7263157894736842</v>
       </c>
       <c r="I6">
-        <v>0.01969293361459967</v>
+        <v>0.130628143642009</v>
       </c>
       <c r="J6">
-        <v>0.6597883597883598</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="K6">
-        <v>0.03311002718976086</v>
+        <v>0.1257629775832786</v>
       </c>
       <c r="L6">
-        <v>0.6788455988455988</v>
+        <v>0.5065759637188209</v>
       </c>
       <c r="M6">
-        <v>0.04676799510847288</v>
+        <v>0.1098604236451927</v>
       </c>
       <c r="N6">
-        <v>0.6597883597883598</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="O6">
-        <v>0.03311002718976086</v>
+        <v>0.1257629775832786</v>
       </c>
       <c r="P6">
-        <v>0.6576653117387307</v>
+        <v>0.5018454561311703</v>
       </c>
       <c r="Q6">
-        <v>0.03136373171651428</v>
+        <v>0.1370108397101837</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>48</v>
       </c>
       <c r="F7">
-        <v>0.9179155118837657</v>
+        <v>0.931547619047619</v>
       </c>
       <c r="G7">
-        <v>0.01296243348706328</v>
+        <v>0.04710473747423934</v>
       </c>
       <c r="H7">
-        <v>0.8947368421052632</v>
+        <v>0.8</v>
       </c>
       <c r="I7">
-        <v>0.01664356663246513</v>
+        <v>0.03938586722919938</v>
       </c>
       <c r="J7">
-        <v>0.662962962962963</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="K7">
-        <v>0.03128411745840102</v>
+        <v>0.06624013211068362</v>
       </c>
       <c r="L7">
-        <v>0.6827994227994227</v>
+        <v>0.5433106575963719</v>
       </c>
       <c r="M7">
-        <v>0.0441886908736302</v>
+        <v>0.06510946075394475</v>
       </c>
       <c r="N7">
-        <v>0.662962962962963</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="O7">
-        <v>0.03128411745840102</v>
+        <v>0.06624013211068362</v>
       </c>
       <c r="P7">
-        <v>0.6611504952858337</v>
+        <v>0.5542800057085771</v>
       </c>
       <c r="Q7">
-        <v>0.02923617905225985</v>
+        <v>0.07020079304549849</v>
       </c>
       <c r="R7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>48</v>
       </c>
       <c r="F8">
-        <v>0.9175174267237759</v>
+        <v>0.931547619047619</v>
       </c>
       <c r="G8">
-        <v>0.03651577647225435</v>
+        <v>0.04710473747423934</v>
       </c>
       <c r="H8">
-        <v>0.8789473684210527</v>
+        <v>0.8</v>
       </c>
       <c r="I8">
-        <v>0.03569647359539615</v>
+        <v>0.03938586722919938</v>
       </c>
       <c r="J8">
-        <v>0.6534391534391535</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="K8">
-        <v>0.03966489907723028</v>
+        <v>0.06624013211068362</v>
       </c>
       <c r="L8">
-        <v>0.672298495155638</v>
+        <v>0.5433106575963719</v>
       </c>
       <c r="M8">
-        <v>0.05339221287350029</v>
+        <v>0.06510946075394475</v>
       </c>
       <c r="N8">
-        <v>0.6534391534391535</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="O8">
-        <v>0.03966489907723028</v>
+        <v>0.06624013211068362</v>
       </c>
       <c r="P8">
-        <v>0.6502858336316983</v>
+        <v>0.5542800057085771</v>
       </c>
       <c r="Q8">
-        <v>0.03971623462340463</v>
+        <v>0.07020079304549849</v>
       </c>
       <c r="R8" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1043,49 +1013,49 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
         <v>48</v>
       </c>
       <c r="F9">
-        <v>0.9160021415973796</v>
+        <v>0.9303571428571429</v>
       </c>
       <c r="G9">
-        <v>0.03391787381596524</v>
+        <v>0.04592793267718458</v>
       </c>
       <c r="H9">
-        <v>0.8578947368421053</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I9">
-        <v>0.0488085183973458</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J9">
-        <v>0.6509259259259259</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="K9">
-        <v>0.04430802318121825</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="L9">
-        <v>0.6438017538017539</v>
+        <v>0.5746031746031746</v>
       </c>
       <c r="M9">
-        <v>0.03620310955936477</v>
+        <v>0.07800097550281197</v>
       </c>
       <c r="N9">
-        <v>0.6509259259259259</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="O9">
-        <v>0.04430802318121825</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="P9">
-        <v>0.6410380292467864</v>
+        <v>0.5849293563579276</v>
       </c>
       <c r="Q9">
-        <v>0.04602539054518649</v>
+        <v>0.08572400972502163</v>
       </c>
       <c r="R9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1093,49 +1063,49 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
         <v>48</v>
       </c>
       <c r="F10">
-        <v>0.9160021415973796</v>
+        <v>0.9303571428571429</v>
       </c>
       <c r="G10">
-        <v>0.03391787381596524</v>
+        <v>0.04590864252022583</v>
       </c>
       <c r="H10">
-        <v>0.8578947368421053</v>
+        <v>0.8</v>
       </c>
       <c r="I10">
-        <v>0.0488085183973458</v>
+        <v>0.03938586722919938</v>
       </c>
       <c r="J10">
-        <v>0.6509259259259259</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="K10">
-        <v>0.04430802318121825</v>
+        <v>0.06624013211068362</v>
       </c>
       <c r="L10">
-        <v>0.6438017538017539</v>
+        <v>0.5433106575963719</v>
       </c>
       <c r="M10">
-        <v>0.03620310955936477</v>
+        <v>0.06510946075394475</v>
       </c>
       <c r="N10">
-        <v>0.6509259259259259</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="O10">
-        <v>0.04430802318121825</v>
+        <v>0.06624013211068362</v>
       </c>
       <c r="P10">
-        <v>0.6410380292467864</v>
+        <v>0.5542800057085771</v>
       </c>
       <c r="Q10">
-        <v>0.04602539054518649</v>
+        <v>0.07020079304549849</v>
       </c>
       <c r="R10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1143,493 +1113,499 @@
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
         <v>48</v>
       </c>
       <c r="F11">
-        <v>0.9158375325438817</v>
+        <v>0.9297619047619048</v>
       </c>
       <c r="G11">
-        <v>0.03394833049657767</v>
+        <v>0.05680860824313107</v>
       </c>
       <c r="H11">
-        <v>0.8578947368421053</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I11">
-        <v>0.0488085183973458</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J11">
-        <v>0.6509259259259259</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="K11">
-        <v>0.04430802318121825</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="L11">
-        <v>0.6438017538017539</v>
+        <v>0.5746031746031746</v>
       </c>
       <c r="M11">
-        <v>0.03620310955936477</v>
+        <v>0.07800097550281197</v>
       </c>
       <c r="N11">
-        <v>0.6509259259259259</v>
+        <v>0.6142857142857142</v>
       </c>
       <c r="O11">
-        <v>0.04430802318121825</v>
+        <v>0.08268454930564449</v>
       </c>
       <c r="P11">
-        <v>0.6410380292467864</v>
+        <v>0.5849293563579276</v>
       </c>
       <c r="Q11">
-        <v>0.04602539054518649</v>
+        <v>0.08572400972502163</v>
       </c>
       <c r="R11" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
       </c>
       <c r="F12">
-        <v>0.9148276224069875</v>
+        <v>0.9282738095238094</v>
       </c>
       <c r="G12">
-        <v>0.01167679465892643</v>
+        <v>0.05904119828762028</v>
       </c>
       <c r="H12">
-        <v>0.8947368421052632</v>
+        <v>0.7789473684210527</v>
       </c>
       <c r="I12">
-        <v>0.01664356663246513</v>
+        <v>0.05156820511122478</v>
       </c>
       <c r="J12">
-        <v>0.662962962962963</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K12">
-        <v>0.03128411745840102</v>
+        <v>0.07824607964359517</v>
       </c>
       <c r="L12">
-        <v>0.6827994227994227</v>
+        <v>0.5335714285714286</v>
       </c>
       <c r="M12">
-        <v>0.0441886908736302</v>
+        <v>0.07338742593737894</v>
       </c>
       <c r="N12">
-        <v>0.662962962962963</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="O12">
-        <v>0.03128411745840102</v>
+        <v>0.07824607964359517</v>
       </c>
       <c r="P12">
-        <v>0.6611504952858337</v>
+        <v>0.5419954648526077</v>
       </c>
       <c r="Q12">
-        <v>0.02923617905225985</v>
+        <v>0.08071369883133521</v>
       </c>
       <c r="R12" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
       </c>
       <c r="F13">
-        <v>0.9145380868396741</v>
+        <v>0.8994047619047618</v>
       </c>
       <c r="G13">
-        <v>0.01154419941508568</v>
+        <v>0.0416092291186199</v>
       </c>
       <c r="H13">
-        <v>0.8789473684210527</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="I13">
-        <v>0.03569647359539615</v>
+        <v>0.06657426652986062</v>
       </c>
       <c r="J13">
-        <v>0.6470899470899472</v>
+        <v>0.6</v>
       </c>
       <c r="K13">
-        <v>0.04871174301157208</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="L13">
-        <v>0.6739249639249639</v>
+        <v>0.5506802721088435</v>
       </c>
       <c r="M13">
-        <v>0.05151591140946652</v>
+        <v>0.08309517544223682</v>
       </c>
       <c r="N13">
-        <v>0.6470899470899472</v>
+        <v>0.6</v>
       </c>
       <c r="O13">
-        <v>0.04871174301157208</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="P13">
-        <v>0.6441757053698673</v>
+        <v>0.5681529581529581</v>
       </c>
       <c r="Q13">
-        <v>0.04897597131399631</v>
+        <v>0.08853798837369412</v>
       </c>
       <c r="R13" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D14" t="s">
         <v>48</v>
       </c>
       <c r="F14">
-        <v>0.9113147728227095</v>
+        <v>0.8979166666666666</v>
       </c>
       <c r="G14">
-        <v>0.0214956398508304</v>
+        <v>0.04431026905030772</v>
       </c>
       <c r="H14">
-        <v>0.8526315789473685</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="I14">
-        <v>0.05418752705782631</v>
+        <v>0.06657426652986062</v>
       </c>
       <c r="J14">
-        <v>0.6153439153439153</v>
+        <v>0.6</v>
       </c>
       <c r="K14">
-        <v>0.05668047297710933</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="L14">
-        <v>0.6080721892486598</v>
+        <v>0.5506802721088435</v>
       </c>
       <c r="M14">
-        <v>0.07553574310289043</v>
+        <v>0.08309517544223682</v>
       </c>
       <c r="N14">
-        <v>0.6153439153439153</v>
+        <v>0.6</v>
       </c>
       <c r="O14">
-        <v>0.05668047297710933</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="P14">
-        <v>0.602230830253829</v>
+        <v>0.5681529581529581</v>
       </c>
       <c r="Q14">
-        <v>0.06625050905072642</v>
+        <v>0.08853798837369412</v>
       </c>
       <c r="R14" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>20</v>
       </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
       <c r="F15">
-        <v>0.9090995449105568</v>
+        <v>0.8976190476190476</v>
       </c>
       <c r="G15">
-        <v>0.02730588427162512</v>
+        <v>0.03459813428050144</v>
       </c>
       <c r="H15">
-        <v>0.8578947368421053</v>
+        <v>0.8</v>
       </c>
       <c r="I15">
-        <v>0.01289205127780624</v>
+        <v>0.06137844099837159</v>
       </c>
       <c r="J15">
-        <v>0.6096560846560847</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="K15">
-        <v>0.04325295696437643</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="L15">
-        <v>0.6368157768157768</v>
+        <v>0.5812925170068028</v>
       </c>
       <c r="M15">
-        <v>0.0855283649859479</v>
+        <v>0.07194693670437292</v>
       </c>
       <c r="N15">
-        <v>0.6096560846560847</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="O15">
-        <v>0.04325295696437643</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="P15">
-        <v>0.6055587381151291</v>
+        <v>0.5982828282828281</v>
       </c>
       <c r="Q15">
-        <v>0.05608914171599728</v>
+        <v>0.07462127517459613</v>
       </c>
       <c r="R15" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
         <v>48</v>
       </c>
       <c r="F16">
-        <v>0.9079980263710423</v>
+        <v>0.8964285714285716</v>
       </c>
       <c r="G16">
-        <v>0.03592503034920711</v>
+        <v>0.04833538583490901</v>
       </c>
       <c r="H16">
-        <v>0.8736842105263157</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="I16">
-        <v>0.0196929336145997</v>
+        <v>0.06657426652986062</v>
       </c>
       <c r="J16">
-        <v>0.6667989417989418</v>
+        <v>0.6</v>
       </c>
       <c r="K16">
-        <v>0.01526846987355352</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="L16">
-        <v>0.6511104239675668</v>
+        <v>0.5506802721088435</v>
       </c>
       <c r="M16">
-        <v>0.02090133105196385</v>
+        <v>0.08309517544223682</v>
       </c>
       <c r="N16">
-        <v>0.6667989417989418</v>
+        <v>0.6</v>
       </c>
       <c r="O16">
-        <v>0.01526846987355352</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="P16">
-        <v>0.6556445853195079</v>
+        <v>0.5681529581529581</v>
       </c>
       <c r="Q16">
-        <v>0.01729078144460951</v>
+        <v>0.08853798837369412</v>
       </c>
       <c r="R16" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
       </c>
       <c r="F17">
-        <v>0.9043589905097841</v>
+        <v>0.89375</v>
       </c>
       <c r="G17">
-        <v>0.03498487822260653</v>
+        <v>0.03964705754952819</v>
       </c>
       <c r="H17">
-        <v>0.8631578947368421</v>
+        <v>0.8</v>
       </c>
       <c r="I17">
-        <v>0.02578410255561241</v>
+        <v>0.06137844099837159</v>
       </c>
       <c r="J17">
-        <v>0.6541005291005292</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="K17">
-        <v>0.0279410670482209</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="L17">
-        <v>0.64506734006734</v>
+        <v>0.5822448979591835</v>
       </c>
       <c r="M17">
-        <v>0.02481820601408739</v>
+        <v>0.07146173509355434</v>
       </c>
       <c r="N17">
-        <v>0.6541005291005292</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="O17">
-        <v>0.0279410670482209</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="P17">
-        <v>0.6455381918849411</v>
+        <v>0.5971036899608327</v>
       </c>
       <c r="Q17">
-        <v>0.02702771426520876</v>
+        <v>0.0751384192665866</v>
       </c>
       <c r="R17" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
         <v>48</v>
       </c>
       <c r="F18">
-        <v>0.9032060972537164</v>
+        <v>0.89375</v>
       </c>
       <c r="G18">
-        <v>0.03580875927251697</v>
+        <v>0.03964705754952819</v>
       </c>
       <c r="H18">
-        <v>0.8631578947368421</v>
+        <v>0.8</v>
       </c>
       <c r="I18">
-        <v>0.02578410255561241</v>
+        <v>0.06137844099837159</v>
       </c>
       <c r="J18">
-        <v>0.6541005291005292</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="K18">
-        <v>0.0279410670482209</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="L18">
-        <v>0.64506734006734</v>
+        <v>0.5822448979591835</v>
       </c>
       <c r="M18">
-        <v>0.02481820601408739</v>
+        <v>0.07146173509355434</v>
       </c>
       <c r="N18">
-        <v>0.6541005291005292</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="O18">
-        <v>0.0279410670482209</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="P18">
-        <v>0.6455381918849411</v>
+        <v>0.5971036899608327</v>
       </c>
       <c r="Q18">
-        <v>0.02702771426520876</v>
+        <v>0.0751384192665866</v>
       </c>
       <c r="R18" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="F19">
-        <v>0.9002518738977072</v>
+        <v>0.89375</v>
       </c>
       <c r="G19">
-        <v>0.03782928207194296</v>
+        <v>0.03964705754952819</v>
       </c>
       <c r="H19">
-        <v>0.8526315789473685</v>
+        <v>0.8</v>
       </c>
       <c r="I19">
-        <v>0.03569647359539616</v>
+        <v>0.06137844099837159</v>
       </c>
       <c r="J19">
-        <v>0.6478835978835977</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="K19">
-        <v>0.04139514284458976</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="L19">
-        <v>0.6392496392496392</v>
+        <v>0.5822448979591835</v>
       </c>
       <c r="M19">
-        <v>0.03497723580091525</v>
+        <v>0.07146173509355434</v>
       </c>
       <c r="N19">
-        <v>0.6478835978835977</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="O19">
-        <v>0.04139514284458976</v>
+        <v>0.0735402152927643</v>
       </c>
       <c r="P19">
-        <v>0.6384303896997394</v>
+        <v>0.5971036899608327</v>
       </c>
       <c r="Q19">
-        <v>0.04140256324174093</v>
+        <v>0.0751384192665866</v>
       </c>
       <c r="R19" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
         <v>48</v>
       </c>
       <c r="F20">
-        <v>0.8987018140589569</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="G20">
-        <v>0.04252142568540716</v>
+        <v>0.05289754729856654</v>
       </c>
       <c r="H20">
-        <v>0.8578947368421053</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="I20">
-        <v>0.03938586722919939</v>
+        <v>0.07735230766683719</v>
       </c>
       <c r="J20">
-        <v>0.6447089947089946</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="K20">
-        <v>0.05332902896882541</v>
+        <v>0.09741558354989897</v>
       </c>
       <c r="L20">
-        <v>0.6445526695526695</v>
+        <v>0.5460544217687074</v>
       </c>
       <c r="M20">
-        <v>0.03428686514507514</v>
+        <v>0.08841956949302698</v>
       </c>
       <c r="N20">
-        <v>0.6447089947089946</v>
+        <v>0.5928571428571429</v>
       </c>
       <c r="O20">
-        <v>0.05332902896882541</v>
+        <v>0.09741558354989897</v>
       </c>
       <c r="P20">
-        <v>0.6363457663767262</v>
+        <v>0.5627272727272726</v>
       </c>
       <c r="Q20">
-        <v>0.0522543785634348</v>
+        <v>0.09497114162111674</v>
       </c>
       <c r="R20" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -1637,49 +1613,49 @@
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="F21">
-        <v>0.8985561014529269</v>
+        <v>0.8919642857142858</v>
       </c>
       <c r="G21">
-        <v>0.04890800867072406</v>
+        <v>0.05075779209195259</v>
       </c>
       <c r="H21">
-        <v>0.8473684210526317</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I21">
-        <v>0.04527539614232961</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J21">
-        <v>0.6275132275132275</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="K21">
-        <v>0.04978608252358833</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="L21">
-        <v>0.6421134421134422</v>
+        <v>0.5922448979591837</v>
       </c>
       <c r="M21">
-        <v>0.03429738344697515</v>
+        <v>0.0700192684189736</v>
       </c>
       <c r="N21">
-        <v>0.6275132275132275</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="O21">
-        <v>0.04978608252358833</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="P21">
-        <v>0.6219078508596421</v>
+        <v>0.6072397443826014</v>
       </c>
       <c r="Q21">
-        <v>0.05142928256295275</v>
+        <v>0.0735107648183627</v>
       </c>
       <c r="R21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -1687,149 +1663,149 @@
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D22" t="s">
         <v>48</v>
       </c>
       <c r="F22">
-        <v>0.8981093054505752</v>
+        <v>0.8919642857142858</v>
       </c>
       <c r="G22">
-        <v>0.04894658560058082</v>
+        <v>0.05075779209195259</v>
       </c>
       <c r="H22">
-        <v>0.8473684210526317</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I22">
-        <v>0.04527539614232961</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J22">
-        <v>0.6275132275132275</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="K22">
-        <v>0.04978608252358833</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="L22">
-        <v>0.6418408575551433</v>
+        <v>0.5922448979591837</v>
       </c>
       <c r="M22">
-        <v>0.03598561205117215</v>
+        <v>0.0700192684189736</v>
       </c>
       <c r="N22">
-        <v>0.6275132275132275</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="O22">
-        <v>0.04978608252358833</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="P22">
-        <v>0.6221014019642944</v>
+        <v>0.6072397443826014</v>
       </c>
       <c r="Q22">
-        <v>0.05119584496834887</v>
+        <v>0.0735107648183627</v>
       </c>
       <c r="R22" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
         <v>48</v>
       </c>
       <c r="F23">
-        <v>0.8970214212228103</v>
+        <v>0.8919642857142858</v>
       </c>
       <c r="G23">
-        <v>0.0381156742988004</v>
+        <v>0.05075779209195259</v>
       </c>
       <c r="H23">
-        <v>0.8631578947368421</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I23">
-        <v>0.02578410255561241</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J23">
-        <v>0.6542328042328042</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="K23">
-        <v>0.03436710569112166</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="L23">
-        <v>0.6450432900432901</v>
+        <v>0.5922448979591837</v>
       </c>
       <c r="M23">
-        <v>0.03040630036027698</v>
+        <v>0.0700192684189736</v>
       </c>
       <c r="N23">
-        <v>0.6542328042328042</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="O23">
-        <v>0.03436710569112166</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="P23">
-        <v>0.6457133028650056</v>
+        <v>0.6072397443826014</v>
       </c>
       <c r="Q23">
-        <v>0.03341243800989287</v>
+        <v>0.0735107648183627</v>
       </c>
       <c r="R23" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
         <v>48</v>
       </c>
       <c r="F24">
-        <v>0.8968277063911984</v>
+        <v>0.8919642857142858</v>
       </c>
       <c r="G24">
-        <v>0.04922920415464806</v>
+        <v>0.05193089938232919</v>
       </c>
       <c r="H24">
-        <v>0.8473684210526317</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="I24">
-        <v>0.04527539614232961</v>
+        <v>0.06657426652986062</v>
       </c>
       <c r="J24">
-        <v>0.6275132275132275</v>
+        <v>0.6</v>
       </c>
       <c r="K24">
-        <v>0.04978608252358833</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="L24">
-        <v>0.6418408575551433</v>
+        <v>0.552721088435374</v>
       </c>
       <c r="M24">
-        <v>0.03598561205117215</v>
+        <v>0.08097124344356506</v>
       </c>
       <c r="N24">
-        <v>0.6275132275132275</v>
+        <v>0.6</v>
       </c>
       <c r="O24">
-        <v>0.04978608252358833</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="P24">
-        <v>0.6221014019642944</v>
+        <v>0.5697113997113997</v>
       </c>
       <c r="Q24">
-        <v>0.05119584496834887</v>
+        <v>0.08685286896259813</v>
       </c>
       <c r="R24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -1837,99 +1813,99 @@
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
         <v>48</v>
       </c>
       <c r="F25">
-        <v>0.8927168892248257</v>
+        <v>0.8901785714285714</v>
       </c>
       <c r="G25">
-        <v>0.05358203885745492</v>
+        <v>0.05721256908428855</v>
       </c>
       <c r="H25">
-        <v>0.8368421052631578</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I25">
-        <v>0.03068922049918581</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J25">
-        <v>0.6207671957671957</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="K25">
-        <v>0.04336446091471173</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="L25">
-        <v>0.6372624201195629</v>
+        <v>0.5922448979591837</v>
       </c>
       <c r="M25">
-        <v>0.0265290548339923</v>
+        <v>0.0700192684189736</v>
       </c>
       <c r="N25">
-        <v>0.6207671957671957</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="O25">
-        <v>0.04336446091471173</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="P25">
-        <v>0.6165127454490568</v>
+        <v>0.6072397443826014</v>
       </c>
       <c r="Q25">
-        <v>0.04172427816514754</v>
+        <v>0.0735107648183627</v>
       </c>
       <c r="R25" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C26" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D26" t="s">
         <v>48</v>
       </c>
       <c r="F26">
-        <v>0.8926311465944401</v>
+        <v>0.887797619047619</v>
       </c>
       <c r="G26">
-        <v>0.03902632427477699</v>
+        <v>0.05942402350195581</v>
       </c>
       <c r="H26">
-        <v>0.8421052631578947</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I26">
-        <v>0.06000923289995466</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J26">
-        <v>0.6288359788359787</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="K26">
-        <v>0.07031067205599918</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="L26">
-        <v>0.6371350871350872</v>
+        <v>0.5922448979591837</v>
       </c>
       <c r="M26">
-        <v>0.04665548552865444</v>
+        <v>0.0700192684189736</v>
       </c>
       <c r="N26">
-        <v>0.6288359788359787</v>
+        <v>0.6357142857142858</v>
       </c>
       <c r="O26">
-        <v>0.07031067205599918</v>
+        <v>0.07284313590846837</v>
       </c>
       <c r="P26">
-        <v>0.6194531145791651</v>
+        <v>0.6072397443826014</v>
       </c>
       <c r="Q26">
-        <v>0.07099664201276312</v>
+        <v>0.0735107648183627</v>
       </c>
       <c r="R26" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1937,49 +1913,49 @@
         <v>21</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D27" t="s">
         <v>48</v>
       </c>
       <c r="F27">
-        <v>0.8903374065675653</v>
+        <v>0.8866071428571427</v>
       </c>
       <c r="G27">
-        <v>0.05373380049058897</v>
+        <v>0.05937033786446386</v>
       </c>
       <c r="H27">
-        <v>0.8315789473684211</v>
+        <v>0.8</v>
       </c>
       <c r="I27">
-        <v>0.03938586722919938</v>
+        <v>0.05156820511122482</v>
       </c>
       <c r="J27">
-        <v>0.642989417989418</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="K27">
-        <v>0.07612476958032645</v>
+        <v>0.06998542122237653</v>
       </c>
       <c r="L27">
-        <v>0.6602164502164503</v>
+        <v>0.5793877551020408</v>
       </c>
       <c r="M27">
-        <v>0.05508661741371674</v>
+        <v>0.06621868084890026</v>
       </c>
       <c r="N27">
-        <v>0.642989417989418</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="O27">
-        <v>0.07612476958032645</v>
+        <v>0.06998542122237653</v>
       </c>
       <c r="P27">
-        <v>0.6381952079077244</v>
+        <v>0.5981467738610596</v>
       </c>
       <c r="Q27">
-        <v>0.07231869315879803</v>
+        <v>0.0701422831822973</v>
       </c>
       <c r="R27" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -1987,137 +1963,149 @@
         <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
         <v>48</v>
       </c>
       <c r="F28">
-        <v>0.887186109011506</v>
+        <v>0.881547619047619</v>
       </c>
       <c r="G28">
-        <v>0.05747577616592311</v>
+        <v>0.06381552032946715</v>
       </c>
       <c r="H28">
-        <v>0.8210526315789475</v>
+        <v>0.7684210526315789</v>
       </c>
       <c r="I28">
-        <v>0.03491183989847788</v>
+        <v>0.05367388961676614</v>
       </c>
       <c r="J28">
-        <v>0.6358465608465609</v>
+        <v>0.65</v>
       </c>
       <c r="K28">
-        <v>0.07837522042754785</v>
+        <v>0.06144518047887593</v>
       </c>
       <c r="L28">
-        <v>0.6554054146911289</v>
+        <v>0.6338095238095238</v>
       </c>
       <c r="M28">
-        <v>0.06132574916275296</v>
+        <v>0.06896382435954944</v>
       </c>
       <c r="N28">
-        <v>0.6358465608465609</v>
+        <v>0.65</v>
       </c>
       <c r="O28">
-        <v>0.07837522042754785</v>
+        <v>0.06144518047887593</v>
       </c>
       <c r="P28">
-        <v>0.6327483391017225</v>
+        <v>0.6299092970521543</v>
       </c>
       <c r="Q28">
-        <v>0.07501307328929185</v>
+        <v>0.06896114017460218</v>
       </c>
       <c r="R28" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>48</v>
       </c>
       <c r="F29">
-        <v>0.8869758991559588</v>
+        <v>0.8800595238095237</v>
       </c>
       <c r="G29">
-        <v>0.073589169622276</v>
+        <v>0.06588481798079748</v>
       </c>
       <c r="H29">
-        <v>0.8210526315789475</v>
+        <v>0.7473684210526317</v>
       </c>
       <c r="I29">
-        <v>0.01969293361459967</v>
+        <v>0.03938586722919939</v>
       </c>
       <c r="J29">
-        <v>0.5779100529100528</v>
+        <v>0.6357142857142857</v>
       </c>
       <c r="K29">
-        <v>0.05993742245887062</v>
+        <v>0.06144518047887593</v>
       </c>
       <c r="L29">
-        <v>0.5743468568468568</v>
+        <v>0.6261904761904761</v>
       </c>
       <c r="M29">
-        <v>0.07591434210658016</v>
+        <v>0.09424482037650901</v>
       </c>
       <c r="N29">
-        <v>0.5779100529100528</v>
+        <v>0.6357142857142857</v>
       </c>
       <c r="O29">
-        <v>0.05993742245887062</v>
+        <v>0.06144518047887593</v>
       </c>
       <c r="P29">
-        <v>0.5634534941036489</v>
+        <v>0.6124489795918368</v>
       </c>
       <c r="Q29">
-        <v>0.0619333563022223</v>
+        <v>0.06795163602457335</v>
       </c>
       <c r="R29" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" t="s">
+        <v>48</v>
       </c>
       <c r="F30">
-        <v>0.8864200942722767</v>
+        <v>0.8770833333333334</v>
       </c>
       <c r="G30">
-        <v>0.0274978453495592</v>
+        <v>0.04182156581653703</v>
       </c>
       <c r="H30">
-        <v>0.8210526315789473</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="I30">
-        <v>0.01969293361459967</v>
+        <v>0.1123902973898033</v>
       </c>
       <c r="J30">
-        <v>0.5505291005291004</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="K30">
-        <v>0.04036797790521159</v>
+        <v>0.1173691194653927</v>
       </c>
       <c r="L30">
-        <v>0.515479969765684</v>
+        <v>0.5147619047619048</v>
       </c>
       <c r="M30">
-        <v>0.03435270565931277</v>
+        <v>0.116591495189092</v>
       </c>
       <c r="N30">
-        <v>0.5505291005291004</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="O30">
-        <v>0.04036797790521159</v>
+        <v>0.1173691194653927</v>
       </c>
       <c r="P30">
-        <v>0.5259416168751208</v>
+        <v>0.5332570603999176</v>
       </c>
       <c r="Q30">
-        <v>0.0390373528753784</v>
+        <v>0.1225624368262967</v>
       </c>
       <c r="R30" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2125,99 +2113,93 @@
         <v>21</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
       </c>
       <c r="F31">
-        <v>0.8839136904761906</v>
+        <v>0.875</v>
       </c>
       <c r="G31">
-        <v>0.05671071677586315</v>
+        <v>0.0613557384764533</v>
       </c>
       <c r="H31">
-        <v>0.7947368421052631</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="I31">
-        <v>0.03491183989847789</v>
+        <v>0.05156820511122479</v>
       </c>
       <c r="J31">
-        <v>0.6772486772486773</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="K31">
-        <v>0.1172289059409796</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="L31">
-        <v>0.6955511948369091</v>
+        <v>0.6352380952380952</v>
       </c>
       <c r="M31">
-        <v>0.1012261785797168</v>
+        <v>0.07135551819813421</v>
       </c>
       <c r="N31">
-        <v>0.6772486772486773</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="O31">
-        <v>0.1172289059409796</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="P31">
-        <v>0.6579174381076194</v>
+        <v>0.6340136054421769</v>
       </c>
       <c r="Q31">
-        <v>0.1067272910446469</v>
+        <v>0.08161082474598763</v>
       </c>
       <c r="R31" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F32">
-        <v>0.8828581139245821</v>
+        <v>0.8744047619047619</v>
       </c>
       <c r="G32">
-        <v>0.05725860597582903</v>
+        <v>0.05289419818670153</v>
       </c>
       <c r="H32">
-        <v>0.8105263157894737</v>
+        <v>0.7684210526315789</v>
       </c>
       <c r="I32">
-        <v>0.0386761538334186</v>
+        <v>0.05367388961676614</v>
       </c>
       <c r="J32">
-        <v>0.6796296296296295</v>
+        <v>0.5214285714285714</v>
       </c>
       <c r="K32">
-        <v>0.1066777415095563</v>
+        <v>0.03642156795423416</v>
       </c>
       <c r="L32">
-        <v>0.6996575646575647</v>
+        <v>0.4842857142857143</v>
       </c>
       <c r="M32">
-        <v>0.09194678522539856</v>
+        <v>0.01999166840205464</v>
       </c>
       <c r="N32">
-        <v>0.6796296296296295</v>
+        <v>0.5214285714285714</v>
       </c>
       <c r="O32">
-        <v>0.1066777415095563</v>
+        <v>0.03642156795423416</v>
       </c>
       <c r="P32">
-        <v>0.6616900524165008</v>
+        <v>0.4894475365903938</v>
       </c>
       <c r="Q32">
-        <v>0.09622474631527933</v>
+        <v>0.03068819068985366</v>
       </c>
       <c r="R32" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2225,99 +2207,93 @@
         <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D33" t="s">
         <v>48</v>
       </c>
       <c r="F33">
-        <v>0.8820064090450996</v>
+        <v>0.8645833333333334</v>
       </c>
       <c r="G33">
-        <v>0.05835791798185831</v>
+        <v>0.06531365106831048</v>
       </c>
       <c r="H33">
-        <v>0.7578947368421053</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="I33">
-        <v>0.0349118398984779</v>
+        <v>0.05156820511122479</v>
       </c>
       <c r="J33">
-        <v>0.6537037037037037</v>
+        <v>0.6357142857142857</v>
       </c>
       <c r="K33">
-        <v>0.1150509300149221</v>
+        <v>0.1020204061220407</v>
       </c>
       <c r="L33">
-        <v>0.648118944547516</v>
+        <v>0.6042857142857143</v>
       </c>
       <c r="M33">
-        <v>0.08525500141565469</v>
+        <v>0.1029320714737077</v>
       </c>
       <c r="N33">
-        <v>0.6537037037037037</v>
+        <v>0.6357142857142857</v>
       </c>
       <c r="O33">
-        <v>0.1150509300149221</v>
+        <v>0.1020204061220407</v>
       </c>
       <c r="P33">
-        <v>0.6208787433190832</v>
+        <v>0.6086394557823129</v>
       </c>
       <c r="Q33">
-        <v>0.08940716170433476</v>
+        <v>0.1057104917648609</v>
       </c>
       <c r="R33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F34">
-        <v>0.8710869394053917</v>
+        <v>0.8568452380952382</v>
       </c>
       <c r="G34">
-        <v>0.06609758268095796</v>
+        <v>0.06514662731014262</v>
       </c>
       <c r="H34">
-        <v>0.7263157894736842</v>
+        <v>0.7052631578947369</v>
       </c>
       <c r="I34">
-        <v>0.06137844099837157</v>
+        <v>0.04210526315789473</v>
       </c>
       <c r="J34">
-        <v>0.6183862433862435</v>
+        <v>0.5642857142857143</v>
       </c>
       <c r="K34">
-        <v>0.05850689246049996</v>
+        <v>0.06925256939166184</v>
       </c>
       <c r="L34">
-        <v>0.6167136831422545</v>
+        <v>0.5045578231292517</v>
       </c>
       <c r="M34">
-        <v>0.05812588666557476</v>
+        <v>0.09820207981402472</v>
       </c>
       <c r="N34">
-        <v>0.6183862433862435</v>
+        <v>0.5642857142857143</v>
       </c>
       <c r="O34">
-        <v>0.05850689246049996</v>
+        <v>0.06925256939166184</v>
       </c>
       <c r="P34">
-        <v>0.5844703333425139</v>
+        <v>0.5091548134405277</v>
       </c>
       <c r="Q34">
-        <v>0.0517486523112877</v>
+        <v>0.06873076597803734</v>
       </c>
       <c r="R34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2325,43 +2301,43 @@
         <v>24</v>
       </c>
       <c r="F35">
-        <v>0.8402677915301922</v>
+        <v>0.8404761904761905</v>
       </c>
       <c r="G35">
-        <v>0.05687588575893067</v>
+        <v>0.07737751823881524</v>
       </c>
       <c r="H35">
-        <v>0.768421052631579</v>
+        <v>0.8105263157894737</v>
       </c>
       <c r="I35">
-        <v>0.03867615383341861</v>
+        <v>0.06315789473684212</v>
       </c>
       <c r="J35">
-        <v>0.5886243386243386</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="K35">
-        <v>0.06920909982722073</v>
+        <v>0.1049781318335648</v>
       </c>
       <c r="L35">
-        <v>0.5973878502449932</v>
+        <v>0.6161904761904762</v>
       </c>
       <c r="M35">
-        <v>0.04296942859290886</v>
+        <v>0.1076380092861434</v>
       </c>
       <c r="N35">
-        <v>0.5886243386243386</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="O35">
-        <v>0.06920909982722073</v>
+        <v>0.1049781318335648</v>
       </c>
       <c r="P35">
-        <v>0.5719125277395954</v>
+        <v>0.633061224489796</v>
       </c>
       <c r="Q35">
-        <v>0.06759936029925484</v>
+        <v>0.1068521677835716</v>
       </c>
       <c r="R35" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2369,43 +2345,43 @@
         <v>25</v>
       </c>
       <c r="F36">
-        <v>0.8380109126984128</v>
+        <v>0.8311011904761905</v>
       </c>
       <c r="G36">
-        <v>0.04619414171300866</v>
+        <v>0.04467508757178304</v>
       </c>
       <c r="H36">
-        <v>0.7684210526315789</v>
+        <v>0.6736842105263158</v>
       </c>
       <c r="I36">
-        <v>0.05619514869490162</v>
+        <v>0.03938586722919939</v>
       </c>
       <c r="J36">
-        <v>0.5891534391534392</v>
+        <v>0.5214285714285715</v>
       </c>
       <c r="K36">
-        <v>0.07945145211857477</v>
+        <v>0.06624013211068359</v>
       </c>
       <c r="L36">
-        <v>0.5999977007119863</v>
+        <v>0.4524943310657596</v>
       </c>
       <c r="M36">
-        <v>0.04977285345594123</v>
+        <v>0.08266741505714319</v>
       </c>
       <c r="N36">
-        <v>0.5891534391534392</v>
+        <v>0.5214285714285715</v>
       </c>
       <c r="O36">
-        <v>0.07945145211857477</v>
+        <v>0.06624013211068359</v>
       </c>
       <c r="P36">
-        <v>0.5728353038846664</v>
+        <v>0.4500932400932401</v>
       </c>
       <c r="Q36">
-        <v>0.07725193613968989</v>
+        <v>0.06415284352209921</v>
       </c>
       <c r="R36" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2413,43 +2389,43 @@
         <v>26</v>
       </c>
       <c r="F37">
-        <v>0.8380109126984128</v>
+        <v>0.8303571428571429</v>
       </c>
       <c r="G37">
-        <v>0.04619414171300866</v>
+        <v>0.04447637608939549</v>
       </c>
       <c r="H37">
-        <v>0.7578947368421053</v>
+        <v>0.6842105263157894</v>
       </c>
       <c r="I37">
-        <v>0.05367388961676614</v>
+        <v>0.04707511531578504</v>
       </c>
       <c r="J37">
-        <v>0.6014550264550265</v>
+        <v>0.5071428571428571</v>
       </c>
       <c r="K37">
-        <v>0.0670174277998027</v>
+        <v>0.06144518047887589</v>
       </c>
       <c r="L37">
-        <v>0.5755871905871907</v>
+        <v>0.4656462585034012</v>
       </c>
       <c r="M37">
-        <v>0.08255138496709735</v>
+        <v>0.07875189099933486</v>
       </c>
       <c r="N37">
-        <v>0.6014550264550265</v>
+        <v>0.5071428571428571</v>
       </c>
       <c r="O37">
-        <v>0.0670174277998027</v>
+        <v>0.06144518047887589</v>
       </c>
       <c r="P37">
-        <v>0.5637530769883712</v>
+        <v>0.4634941249226964</v>
       </c>
       <c r="Q37">
-        <v>0.06290446478723677</v>
+        <v>0.06187333286354044</v>
       </c>
       <c r="R37" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2457,43 +2433,43 @@
         <v>27</v>
       </c>
       <c r="F38">
-        <v>0.8359605562904175</v>
+        <v>0.8255952380952382</v>
       </c>
       <c r="G38">
-        <v>0.04934042605974912</v>
+        <v>0.03836458445888535</v>
       </c>
       <c r="H38">
-        <v>0.736842105263158</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="I38">
-        <v>0.05263157894736841</v>
+        <v>0.06657426652986059</v>
       </c>
       <c r="J38">
-        <v>0.5829365079365079</v>
+        <v>0.5642857142857143</v>
       </c>
       <c r="K38">
-        <v>0.07990293935652838</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="L38">
-        <v>0.5673825255780143</v>
+        <v>0.5026530612244897</v>
       </c>
       <c r="M38">
-        <v>0.09313808319903362</v>
+        <v>0.09446856257805004</v>
       </c>
       <c r="N38">
-        <v>0.5829365079365079</v>
+        <v>0.5642857142857143</v>
       </c>
       <c r="O38">
-        <v>0.07990293935652838</v>
+        <v>0.08864052604279184</v>
       </c>
       <c r="P38">
-        <v>0.5361000535017418</v>
+        <v>0.5234405277262421</v>
       </c>
       <c r="Q38">
-        <v>0.08049508680107495</v>
+        <v>0.08959243562949354</v>
       </c>
       <c r="R38" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2501,43 +2477,43 @@
         <v>28</v>
       </c>
       <c r="F39">
-        <v>0.8296682229990762</v>
+        <v>0.8255952380952382</v>
       </c>
       <c r="G39">
-        <v>0.05088015424167996</v>
+        <v>0.03836458445888535</v>
       </c>
       <c r="H39">
-        <v>0.7736842105263159</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="I39">
-        <v>0.03938586722919938</v>
+        <v>0.0332871332649303</v>
       </c>
       <c r="J39">
-        <v>0.5809523809523809</v>
+        <v>0.55</v>
       </c>
       <c r="K39">
-        <v>0.04638615617842048</v>
+        <v>0.04844521416518047</v>
       </c>
       <c r="L39">
-        <v>0.5868669690098262</v>
+        <v>0.4758503401360544</v>
       </c>
       <c r="M39">
-        <v>0.04676900000825611</v>
+        <v>0.08218238932679651</v>
       </c>
       <c r="N39">
-        <v>0.5809523809523809</v>
+        <v>0.55</v>
       </c>
       <c r="O39">
-        <v>0.04638615617842048</v>
+        <v>0.04844521416518047</v>
       </c>
       <c r="P39">
-        <v>0.5639232460661032</v>
+        <v>0.4909606266749124</v>
       </c>
       <c r="Q39">
-        <v>0.05057530283953594</v>
+        <v>0.04885786475349964</v>
       </c>
       <c r="R39" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2545,43 +2521,43 @@
         <v>29</v>
       </c>
       <c r="F40">
-        <v>0.8296682229990762</v>
+        <v>0.8236607142857142</v>
       </c>
       <c r="G40">
-        <v>0.05088015424167996</v>
+        <v>0.05056021196567125</v>
       </c>
       <c r="H40">
-        <v>0.7578947368421053</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="I40">
-        <v>0.03068922049918581</v>
+        <v>0.05367388961676615</v>
       </c>
       <c r="J40">
-        <v>0.6075396825396826</v>
+        <v>0.55</v>
       </c>
       <c r="K40">
-        <v>0.0599245767651196</v>
+        <v>0.06624013211068359</v>
       </c>
       <c r="L40">
-        <v>0.5978144078144079</v>
+        <v>0.4940816326530612</v>
       </c>
       <c r="M40">
-        <v>0.03509501191001212</v>
+        <v>0.07826251964754104</v>
       </c>
       <c r="N40">
-        <v>0.590079365079365</v>
+        <v>0.55</v>
       </c>
       <c r="O40">
-        <v>0.06845209339714162</v>
+        <v>0.06624013211068359</v>
       </c>
       <c r="P40">
-        <v>0.5560938923477623</v>
+        <v>0.5057081014223872</v>
       </c>
       <c r="Q40">
-        <v>0.03705042442488893</v>
+        <v>0.06161043927694827</v>
       </c>
       <c r="R40" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2589,43 +2565,43 @@
         <v>30</v>
       </c>
       <c r="F41">
-        <v>0.8243699084572101</v>
+        <v>0.8236607142857142</v>
       </c>
       <c r="G41">
-        <v>0.06144936884951824</v>
+        <v>0.05056021196567125</v>
       </c>
       <c r="H41">
-        <v>0.7842105263157896</v>
+        <v>0.6947368421052632</v>
       </c>
       <c r="I41">
-        <v>0.05102820902543506</v>
+        <v>0.03938586722919938</v>
       </c>
       <c r="J41">
-        <v>0.6137566137566137</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="K41">
-        <v>0.08053806901369458</v>
+        <v>0.06624013211068359</v>
       </c>
       <c r="L41">
-        <v>0.5975549054120484</v>
+        <v>0.4764625850340136</v>
       </c>
       <c r="M41">
-        <v>0.0709596690631268</v>
+        <v>0.09727805527428657</v>
       </c>
       <c r="N41">
-        <v>0.6137566137566137</v>
+        <v>0.5571428571428572</v>
       </c>
       <c r="O41">
-        <v>0.08053806901369458</v>
+        <v>0.06624013211068359</v>
       </c>
       <c r="P41">
-        <v>0.581701675608181</v>
+        <v>0.4888600288600289</v>
       </c>
       <c r="Q41">
-        <v>0.07826921567542026</v>
+        <v>0.06200477630327463</v>
       </c>
       <c r="R41" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -2633,43 +2609,43 @@
         <v>31</v>
       </c>
       <c r="F42">
-        <v>0.823498755983875</v>
+        <v>0.8208333333333334</v>
       </c>
       <c r="G42">
-        <v>0.04123628056686283</v>
+        <v>0.05034602488997739</v>
       </c>
       <c r="H42">
-        <v>0.7526315789473685</v>
+        <v>0.7684210526315789</v>
       </c>
       <c r="I42">
-        <v>0.06359497880839246</v>
+        <v>0.07877173445839876</v>
       </c>
       <c r="J42">
-        <v>0.5862433862433862</v>
+        <v>0.6928571428571428</v>
       </c>
       <c r="K42">
-        <v>0.09621286140655208</v>
+        <v>0.08630747123996123</v>
       </c>
       <c r="L42">
-        <v>0.6111707200362663</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="M42">
-        <v>0.05933504915735573</v>
+        <v>0.09563014543831504</v>
       </c>
       <c r="N42">
-        <v>0.5862433862433862</v>
+        <v>0.6928571428571428</v>
       </c>
       <c r="O42">
-        <v>0.09621286140655208</v>
+        <v>0.08630747123996123</v>
       </c>
       <c r="P42">
-        <v>0.5578526507817125</v>
+        <v>0.6625396825396825</v>
       </c>
       <c r="Q42">
-        <v>0.09353216497465822</v>
+        <v>0.09538485075659395</v>
       </c>
       <c r="R42" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -2677,43 +2653,43 @@
         <v>32</v>
       </c>
       <c r="F43">
-        <v>0.8140011652809271</v>
+        <v>0.8</v>
       </c>
       <c r="G43">
-        <v>0.0502712906835928</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="H43">
-        <v>0.7473684210526317</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="I43">
-        <v>0.0488085183973458</v>
+        <v>0.05156820511122479</v>
       </c>
       <c r="J43">
-        <v>0.5748677248677249</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="K43">
-        <v>0.06778684333591337</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="L43">
-        <v>0.5646611721611722</v>
+        <v>0.6404761904761904</v>
       </c>
       <c r="M43">
-        <v>0.070018941272353</v>
+        <v>0.06824658505655858</v>
       </c>
       <c r="N43">
-        <v>0.5748677248677249</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="O43">
-        <v>0.06778684333591337</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="P43">
-        <v>0.5445323673819915</v>
+        <v>0.6343537414965986</v>
       </c>
       <c r="Q43">
-        <v>0.075313333550891</v>
+        <v>0.08142490571940929</v>
       </c>
       <c r="R43" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -2721,43 +2697,43 @@
         <v>33</v>
       </c>
       <c r="F44">
-        <v>0.8008963477366254</v>
+        <v>0.8</v>
       </c>
       <c r="G44">
-        <v>0.06886428869357243</v>
+        <v>0.04677071733467426</v>
       </c>
       <c r="H44">
-        <v>0.7473684210526315</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="I44">
-        <v>0.03938586722919939</v>
+        <v>0.05156820511122479</v>
       </c>
       <c r="J44">
-        <v>0.6529100529100529</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="K44">
-        <v>0.1168337655636852</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="L44">
-        <v>0.6440311276025562</v>
+        <v>0.6404761904761904</v>
       </c>
       <c r="M44">
-        <v>0.08939221845239397</v>
+        <v>0.06824658505655858</v>
       </c>
       <c r="N44">
-        <v>0.6529100529100529</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="O44">
-        <v>0.1168337655636852</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="P44">
-        <v>0.61707817045836</v>
+        <v>0.6343537414965986</v>
       </c>
       <c r="Q44">
-        <v>0.09310628410014732</v>
+        <v>0.08142490571940929</v>
       </c>
       <c r="R44" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -2765,43 +2741,43 @@
         <v>34</v>
       </c>
       <c r="F45">
-        <v>0.7964814814814816</v>
+        <v>0.7985119047619047</v>
       </c>
       <c r="G45">
-        <v>0.06789496674214027</v>
+        <v>0.04234774983514205</v>
       </c>
       <c r="H45">
-        <v>0.7473684210526315</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="I45">
-        <v>0.03938586722919939</v>
+        <v>0.05156820511122479</v>
       </c>
       <c r="J45">
-        <v>0.6529100529100529</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="K45">
-        <v>0.1168337655636852</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="L45">
-        <v>0.6440311276025562</v>
+        <v>0.6404761904761904</v>
       </c>
       <c r="M45">
-        <v>0.08939221845239397</v>
+        <v>0.06824658505655858</v>
       </c>
       <c r="N45">
-        <v>0.6529100529100529</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="O45">
-        <v>0.1168337655636852</v>
+        <v>0.08017837257372733</v>
       </c>
       <c r="P45">
-        <v>0.61707817045836</v>
+        <v>0.6343537414965986</v>
       </c>
       <c r="Q45">
-        <v>0.09310628410014732</v>
+        <v>0.08142490571940929</v>
       </c>
       <c r="R45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -2809,43 +2785,43 @@
         <v>35</v>
       </c>
       <c r="F46">
-        <v>0.7964814814814816</v>
+        <v>0.7952380952380953</v>
       </c>
       <c r="G46">
-        <v>0.06789496674214027</v>
+        <v>0.03782924248913251</v>
       </c>
       <c r="H46">
-        <v>0.7473684210526315</v>
+        <v>0.2421052631578947</v>
       </c>
       <c r="I46">
-        <v>0.03938586722919939</v>
+        <v>0.06315789473684211</v>
       </c>
       <c r="J46">
-        <v>0.6529100529100529</v>
+        <v>0.1642857142857143</v>
       </c>
       <c r="K46">
-        <v>0.1168337655636852</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="L46">
-        <v>0.6440311276025562</v>
+        <v>0.05977443609022557</v>
       </c>
       <c r="M46">
-        <v>0.08939221845239397</v>
+        <v>0.05939849624060151</v>
       </c>
       <c r="N46">
-        <v>0.6529100529100529</v>
+        <v>0.1642857142857143</v>
       </c>
       <c r="O46">
-        <v>0.1168337655636852</v>
+        <v>0.04285714285714286</v>
       </c>
       <c r="P46">
-        <v>0.61707817045836</v>
+        <v>0.07566992014196983</v>
       </c>
       <c r="Q46">
-        <v>0.09310628410014732</v>
+        <v>0.05196095829636202</v>
       </c>
       <c r="R46" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -2853,43 +2829,43 @@
         <v>36</v>
       </c>
       <c r="F47">
-        <v>0.7818518518518518</v>
+        <v>0.7922619047619047</v>
       </c>
       <c r="G47">
-        <v>0.0281238473319657</v>
+        <v>0.04831705684185874</v>
       </c>
       <c r="H47">
-        <v>0.7684210526315789</v>
+        <v>0.6842105263157896</v>
       </c>
       <c r="I47">
-        <v>0.03491183989847789</v>
+        <v>0.04707511531578504</v>
       </c>
       <c r="J47">
-        <v>0.628042328042328</v>
+        <v>0.507142857142857</v>
       </c>
       <c r="K47">
-        <v>0.04887848041930682</v>
+        <v>0.07284313590846835</v>
       </c>
       <c r="L47">
-        <v>0.6207263107263108</v>
+        <v>0.4448752834467119</v>
       </c>
       <c r="M47">
-        <v>0.02241091473999548</v>
+        <v>0.1031784006676982</v>
       </c>
       <c r="N47">
-        <v>0.628042328042328</v>
+        <v>0.507142857142857</v>
       </c>
       <c r="O47">
-        <v>0.04887848041930682</v>
+        <v>0.07284313590846835</v>
       </c>
       <c r="P47">
-        <v>0.6153612556133565</v>
+        <v>0.448089529518101</v>
       </c>
       <c r="Q47">
-        <v>0.03432237959476282</v>
+        <v>0.08063299841345903</v>
       </c>
       <c r="R47" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -2897,43 +2873,43 @@
         <v>37</v>
       </c>
       <c r="F48">
-        <v>0.7149057539682538</v>
+        <v>0.7910714285714285</v>
       </c>
       <c r="G48">
-        <v>0.07611806271236123</v>
+        <v>0.04142788724120314</v>
       </c>
       <c r="H48">
-        <v>0.2105263157894737</v>
+        <v>0.7052631578947368</v>
       </c>
       <c r="I48">
-        <v>0.02353755765789252</v>
+        <v>0.05367388961676616</v>
       </c>
       <c r="J48">
-        <v>0.1476190476190476</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="K48">
-        <v>0.009523809523809523</v>
+        <v>0.08268454930564448</v>
       </c>
       <c r="L48">
-        <v>0.03120300751879699</v>
+        <v>0.4946712018140589</v>
       </c>
       <c r="M48">
-        <v>0.004987405699782556</v>
+        <v>0.07268385520012217</v>
       </c>
       <c r="N48">
-        <v>0.1476190476190476</v>
+        <v>0.5428571428571429</v>
       </c>
       <c r="O48">
-        <v>0.009523809523809523</v>
+        <v>0.08268454930564448</v>
       </c>
       <c r="P48">
-        <v>0.05142387266346563</v>
+        <v>0.4837605251890966</v>
       </c>
       <c r="Q48">
-        <v>0.007282123740377833</v>
+        <v>0.08178041036633101</v>
       </c>
       <c r="R48" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
